--- a/artfynd/A 18303-2024 artfynd.xlsx
+++ b/artfynd/A 18303-2024 artfynd.xlsx
@@ -1280,10 +1280,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122152039</v>
+        <v>122152076</v>
       </c>
       <c r="B7" t="n">
-        <v>79727</v>
+        <v>79726</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1296,34 +1296,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Brynje, Jmt</t>
+          <t>Bergsvik, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>479768</v>
+        <v>479653</v>
       </c>
       <c r="R7" t="n">
-        <v>6951511</v>
+        <v>6951307</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1382,7 +1382,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122152024</v>
+        <v>122152081</v>
       </c>
       <c r="B8" t="n">
         <v>79727</v>
@@ -1422,10 +1422,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>479764</v>
+        <v>479613</v>
       </c>
       <c r="R8" t="n">
-        <v>6951289</v>
+        <v>6951267</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1484,10 +1484,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122152050</v>
+        <v>122154343</v>
       </c>
       <c r="B9" t="n">
-        <v>79727</v>
+        <v>94201</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1496,25 +1496,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2081</v>
+        <v>2387</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Källpraktmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Pseudobryum cinclidioides</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Huebener) T.J.Kop.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1524,10 +1524,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>479716</v>
+        <v>479547</v>
       </c>
       <c r="R9" t="n">
-        <v>6951549</v>
+        <v>6951577</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1554,12 +1554,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-10-05</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-10-05</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1574,22 +1574,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122154346</v>
+        <v>122152142</v>
       </c>
       <c r="B10" t="n">
-        <v>57527</v>
+        <v>78645</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1602,34 +1602,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Brynje, Jmt</t>
+          <t>Bergsvik, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>479569</v>
+        <v>479790</v>
       </c>
       <c r="R10" t="n">
-        <v>6951576</v>
+        <v>6951160</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1656,12 +1656,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-10-05</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-10-05</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1676,22 +1676,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122152033</v>
+        <v>122152031</v>
       </c>
       <c r="B11" t="n">
-        <v>79726</v>
+        <v>79727</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1704,21 +1704,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1790,10 +1790,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122152023</v>
+        <v>122152042</v>
       </c>
       <c r="B12" t="n">
-        <v>56576</v>
+        <v>79755</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1802,42 +1802,38 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>102612</v>
+        <v>6462</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Bergsvik, Jmt</t>
+          <t>Brynje, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>479776</v>
+        <v>479757</v>
       </c>
       <c r="R12" t="n">
-        <v>6951285</v>
+        <v>6951495</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1896,10 +1892,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122152071</v>
+        <v>122152028</v>
       </c>
       <c r="B13" t="n">
-        <v>79726</v>
+        <v>78645</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1912,21 +1908,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1936,10 +1932,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>479656</v>
+        <v>479733</v>
       </c>
       <c r="R13" t="n">
-        <v>6951332</v>
+        <v>6951321</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1998,10 +1994,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122152037</v>
+        <v>122152034</v>
       </c>
       <c r="B14" t="n">
-        <v>79755</v>
+        <v>79726</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2010,25 +2006,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2038,10 +2034,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>479767</v>
+        <v>479844</v>
       </c>
       <c r="R14" t="n">
-        <v>6951509</v>
+        <v>6951363</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2100,10 +2096,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122152052</v>
+        <v>122152039</v>
       </c>
       <c r="B15" t="n">
-        <v>79726</v>
+        <v>79727</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2116,21 +2112,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2140,10 +2136,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>479717</v>
+        <v>479768</v>
       </c>
       <c r="R15" t="n">
-        <v>6951549</v>
+        <v>6951511</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2304,7 +2300,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122152049</v>
+        <v>122152033</v>
       </c>
       <c r="B17" t="n">
         <v>79726</v>
@@ -2344,10 +2340,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>479749</v>
+        <v>479817</v>
       </c>
       <c r="R17" t="n">
-        <v>6951522</v>
+        <v>6951441</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2406,7 +2402,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122152026</v>
+        <v>122152045</v>
       </c>
       <c r="B18" t="n">
         <v>79726</v>
@@ -2442,14 +2438,14 @@
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Bergsvik, Jmt</t>
+          <t>Brynje, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>479764</v>
+        <v>479758</v>
       </c>
       <c r="R18" t="n">
-        <v>6951290</v>
+        <v>6951496</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2508,10 +2504,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122152055</v>
+        <v>122152050</v>
       </c>
       <c r="B19" t="n">
-        <v>90779</v>
+        <v>79727</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2524,21 +2520,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>2081</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2548,10 +2544,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>479734</v>
+        <v>479716</v>
       </c>
       <c r="R19" t="n">
-        <v>6951563</v>
+        <v>6951549</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2610,10 +2606,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122152045</v>
+        <v>122152074</v>
       </c>
       <c r="B20" t="n">
-        <v>79726</v>
+        <v>79727</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2626,34 +2622,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Brynje, Jmt</t>
+          <t>Bergsvik, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>479758</v>
+        <v>479654</v>
       </c>
       <c r="R20" t="n">
-        <v>6951496</v>
+        <v>6951309</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2712,7 +2708,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122152041</v>
+        <v>122152052</v>
       </c>
       <c r="B21" t="n">
         <v>79726</v>
@@ -2752,10 +2748,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>479769</v>
+        <v>479717</v>
       </c>
       <c r="R21" t="n">
-        <v>6951516</v>
+        <v>6951549</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2814,10 +2810,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122152079</v>
+        <v>122152054</v>
       </c>
       <c r="B22" t="n">
-        <v>79727</v>
+        <v>79726</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2830,34 +2826,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Bergsvik, Jmt</t>
+          <t>Brynje, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>479619</v>
+        <v>479731</v>
       </c>
       <c r="R22" t="n">
-        <v>6951287</v>
+        <v>6951554</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2916,7 +2912,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122152073</v>
+        <v>122152079</v>
       </c>
       <c r="B23" t="n">
         <v>79727</v>
@@ -2956,10 +2952,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>479656</v>
+        <v>479619</v>
       </c>
       <c r="R23" t="n">
-        <v>6951332</v>
+        <v>6951287</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3018,10 +3014,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122152028</v>
+        <v>122154345</v>
       </c>
       <c r="B24" t="n">
-        <v>78645</v>
+        <v>97129</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3030,38 +3026,38 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Bergsvik, Jmt</t>
+          <t>Brynje, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>479733</v>
+        <v>479596</v>
       </c>
       <c r="R24" t="n">
-        <v>6951321</v>
+        <v>6951595</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3088,12 +3084,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-10-05</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-10-05</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3108,22 +3104,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122152076</v>
+        <v>122152023</v>
       </c>
       <c r="B25" t="n">
-        <v>79726</v>
+        <v>56576</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3136,34 +3132,38 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>102612</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Bergsvik, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>479653</v>
+        <v>479776</v>
       </c>
       <c r="R25" t="n">
-        <v>6951307</v>
+        <v>6951285</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3222,10 +3222,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122152031</v>
+        <v>122152041</v>
       </c>
       <c r="B26" t="n">
-        <v>79727</v>
+        <v>79726</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3238,21 +3238,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3262,10 +3262,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>479817</v>
+        <v>479769</v>
       </c>
       <c r="R26" t="n">
-        <v>6951441</v>
+        <v>6951516</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3324,7 +3324,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122152054</v>
+        <v>122152026</v>
       </c>
       <c r="B27" t="n">
         <v>79726</v>
@@ -3360,14 +3360,14 @@
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Brynje, Jmt</t>
+          <t>Bergsvik, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>479731</v>
+        <v>479764</v>
       </c>
       <c r="R27" t="n">
-        <v>6951554</v>
+        <v>6951290</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3426,10 +3426,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122152142</v>
+        <v>122152024</v>
       </c>
       <c r="B28" t="n">
-        <v>78645</v>
+        <v>79727</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3442,21 +3442,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3466,10 +3466,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>479790</v>
+        <v>479764</v>
       </c>
       <c r="R28" t="n">
-        <v>6951160</v>
+        <v>6951289</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3496,12 +3496,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3528,10 +3528,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122152074</v>
+        <v>122152047</v>
       </c>
       <c r="B29" t="n">
-        <v>79727</v>
+        <v>79755</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3540,38 +3540,38 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2081</v>
+        <v>6462</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Bergsvik, Jmt</t>
+          <t>Brynje, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>479654</v>
+        <v>479750</v>
       </c>
       <c r="R29" t="n">
-        <v>6951309</v>
+        <v>6951517</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3630,7 +3630,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122152077</v>
+        <v>122152071</v>
       </c>
       <c r="B30" t="n">
         <v>79726</v>
@@ -3670,10 +3670,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>479619</v>
+        <v>479656</v>
       </c>
       <c r="R30" t="n">
-        <v>6951287</v>
+        <v>6951332</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3732,10 +3732,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122152042</v>
+        <v>122152068</v>
       </c>
       <c r="B31" t="n">
-        <v>79755</v>
+        <v>95722</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3744,25 +3744,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6462</v>
+        <v>53</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3772,10 +3772,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>479757</v>
+        <v>479630</v>
       </c>
       <c r="R31" t="n">
-        <v>6951495</v>
+        <v>6951446</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3808,6 +3808,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2024-08-30</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>På murken granlåga i gransumpskog.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3834,10 +3839,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122154343</v>
+        <v>122152077</v>
       </c>
       <c r="B32" t="n">
-        <v>94201</v>
+        <v>79726</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3846,38 +3851,38 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>2387</v>
+        <v>6458</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Källpraktmossa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Pseudobryum cinclidioides</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Huebener) T.J.Kop.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Brynje, Jmt</t>
+          <t>Bergsvik, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>479547</v>
+        <v>479619</v>
       </c>
       <c r="R32" t="n">
-        <v>6951577</v>
+        <v>6951287</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -3904,12 +3909,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2024-10-05</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2024-10-05</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3924,22 +3929,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122152057</v>
+        <v>122154346</v>
       </c>
       <c r="B33" t="n">
-        <v>74752</v>
+        <v>57527</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3952,21 +3957,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1467</v>
+        <v>103021</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3976,10 +3981,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>479727</v>
+        <v>479569</v>
       </c>
       <c r="R33" t="n">
-        <v>6951580</v>
+        <v>6951576</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4006,17 +4011,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-10-05</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>På granstubbe intill bäck.</t>
+          <t>2024-10-05</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4031,22 +4031,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122152044</v>
+        <v>122152029</v>
       </c>
       <c r="B34" t="n">
-        <v>79727</v>
+        <v>79755</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4055,25 +4055,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>2081</v>
+        <v>6462</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4083,10 +4083,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>479757</v>
+        <v>479816</v>
       </c>
       <c r="R34" t="n">
-        <v>6951495</v>
+        <v>6951443</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4145,10 +4145,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122152064</v>
+        <v>122152021</v>
       </c>
       <c r="B35" t="n">
-        <v>98511</v>
+        <v>56584</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4161,34 +4161,38 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>219880</v>
+        <v>100138</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Brynje, Jmt</t>
+          <t>Bergsvik, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>479647</v>
+        <v>479770</v>
       </c>
       <c r="R35" t="n">
-        <v>6951498</v>
+        <v>6951296</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4221,6 +4225,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2024-08-30</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Uppflog.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4247,10 +4256,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122154345</v>
+        <v>122152049</v>
       </c>
       <c r="B36" t="n">
-        <v>97129</v>
+        <v>79726</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4259,25 +4268,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>221945</v>
+        <v>6458</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4287,10 +4296,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>479596</v>
+        <v>479749</v>
       </c>
       <c r="R36" t="n">
-        <v>6951595</v>
+        <v>6951522</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4317,12 +4326,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2024-10-05</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2024-10-05</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4337,22 +4346,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122152068</v>
+        <v>122152073</v>
       </c>
       <c r="B37" t="n">
-        <v>95722</v>
+        <v>79727</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4365,34 +4374,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>53</v>
+        <v>2081</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Brynje, Jmt</t>
+          <t>Bergsvik, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>479630</v>
+        <v>479656</v>
       </c>
       <c r="R37" t="n">
-        <v>6951446</v>
+        <v>6951332</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4425,11 +4434,6 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2024-08-30</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>På murken granlåga i gransumpskog.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4456,10 +4460,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122152081</v>
+        <v>122152057</v>
       </c>
       <c r="B38" t="n">
-        <v>79727</v>
+        <v>74752</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4472,34 +4476,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>2081</v>
+        <v>1467</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Bergsvik, Jmt</t>
+          <t>Brynje, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>479613</v>
+        <v>479727</v>
       </c>
       <c r="R38" t="n">
-        <v>6951267</v>
+        <v>6951580</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4532,6 +4536,11 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2024-08-30</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>På granstubbe intill bäck.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4558,10 +4567,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122152047</v>
+        <v>122152055</v>
       </c>
       <c r="B39" t="n">
-        <v>79755</v>
+        <v>90779</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4570,25 +4579,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6462</v>
+        <v>1202</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4598,10 +4607,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>479750</v>
+        <v>479734</v>
       </c>
       <c r="R39" t="n">
-        <v>6951517</v>
+        <v>6951563</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4660,10 +4669,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122152029</v>
+        <v>122152044</v>
       </c>
       <c r="B40" t="n">
-        <v>79755</v>
+        <v>79727</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4672,25 +4681,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6462</v>
+        <v>2081</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4700,10 +4709,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>479816</v>
+        <v>479757</v>
       </c>
       <c r="R40" t="n">
-        <v>6951443</v>
+        <v>6951495</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4762,10 +4771,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122152021</v>
+        <v>122152064</v>
       </c>
       <c r="B41" t="n">
-        <v>56584</v>
+        <v>98511</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4778,38 +4787,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100138</v>
+        <v>219880</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) All.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Bergsvik, Jmt</t>
+          <t>Brynje, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>479770</v>
+        <v>479647</v>
       </c>
       <c r="R41" t="n">
-        <v>6951296</v>
+        <v>6951498</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -4842,11 +4847,6 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2024-08-30</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Uppflog.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4873,10 +4873,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122152034</v>
+        <v>122152037</v>
       </c>
       <c r="B42" t="n">
-        <v>79726</v>
+        <v>79755</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4885,25 +4885,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4913,10 +4913,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>479844</v>
+        <v>479767</v>
       </c>
       <c r="R42" t="n">
-        <v>6951363</v>
+        <v>6951509</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>

--- a/artfynd/A 18303-2024 artfynd.xlsx
+++ b/artfynd/A 18303-2024 artfynd.xlsx
@@ -1994,10 +1994,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122152034</v>
+        <v>122152039</v>
       </c>
       <c r="B14" t="n">
-        <v>79726</v>
+        <v>79727</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2010,21 +2010,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2034,10 +2034,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>479844</v>
+        <v>479768</v>
       </c>
       <c r="R14" t="n">
-        <v>6951363</v>
+        <v>6951511</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2096,10 +2096,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122152039</v>
+        <v>122152034</v>
       </c>
       <c r="B15" t="n">
-        <v>79727</v>
+        <v>79726</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2112,21 +2112,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2136,10 +2136,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>479768</v>
+        <v>479844</v>
       </c>
       <c r="R15" t="n">
-        <v>6951511</v>
+        <v>6951363</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2504,10 +2504,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122152050</v>
+        <v>122152052</v>
       </c>
       <c r="B19" t="n">
-        <v>79727</v>
+        <v>79726</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2520,21 +2520,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2544,7 +2544,7 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>479716</v>
+        <v>479717</v>
       </c>
       <c r="R19" t="n">
         <v>6951549</v>
@@ -2606,7 +2606,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122152074</v>
+        <v>122152050</v>
       </c>
       <c r="B20" t="n">
         <v>79727</v>
@@ -2642,14 +2642,14 @@
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Bergsvik, Jmt</t>
+          <t>Brynje, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>479654</v>
+        <v>479716</v>
       </c>
       <c r="R20" t="n">
-        <v>6951309</v>
+        <v>6951549</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2708,10 +2708,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122152052</v>
+        <v>122152074</v>
       </c>
       <c r="B21" t="n">
-        <v>79726</v>
+        <v>79727</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2724,34 +2724,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Brynje, Jmt</t>
+          <t>Bergsvik, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>479717</v>
+        <v>479654</v>
       </c>
       <c r="R21" t="n">
-        <v>6951549</v>
+        <v>6951309</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -3630,7 +3630,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122152071</v>
+        <v>122152077</v>
       </c>
       <c r="B30" t="n">
         <v>79726</v>
@@ -3670,10 +3670,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>479656</v>
+        <v>479619</v>
       </c>
       <c r="R30" t="n">
-        <v>6951332</v>
+        <v>6951287</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3839,7 +3839,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122152077</v>
+        <v>122152071</v>
       </c>
       <c r="B32" t="n">
         <v>79726</v>
@@ -3879,10 +3879,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>479619</v>
+        <v>479656</v>
       </c>
       <c r="R32" t="n">
-        <v>6951287</v>
+        <v>6951332</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>

--- a/artfynd/A 18303-2024 artfynd.xlsx
+++ b/artfynd/A 18303-2024 artfynd.xlsx
@@ -1280,10 +1280,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122152076</v>
+        <v>122152077</v>
       </c>
       <c r="B7" t="n">
-        <v>79726</v>
+        <v>79727</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1320,10 +1320,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>479653</v>
+        <v>479619</v>
       </c>
       <c r="R7" t="n">
-        <v>6951307</v>
+        <v>6951287</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1382,10 +1382,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122152081</v>
+        <v>122152074</v>
       </c>
       <c r="B8" t="n">
-        <v>79727</v>
+        <v>79728</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1422,10 +1422,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>479613</v>
+        <v>479654</v>
       </c>
       <c r="R8" t="n">
-        <v>6951267</v>
+        <v>6951309</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1484,10 +1484,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122154343</v>
+        <v>122152045</v>
       </c>
       <c r="B9" t="n">
-        <v>94201</v>
+        <v>79727</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1496,25 +1496,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2387</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Källpraktmossa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pseudobryum cinclidioides</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Huebener) T.J.Kop.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1524,10 +1524,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>479547</v>
+        <v>479758</v>
       </c>
       <c r="R9" t="n">
-        <v>6951577</v>
+        <v>6951496</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1554,12 +1554,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-10-05</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-10-05</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1574,22 +1574,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122152142</v>
+        <v>122152021</v>
       </c>
       <c r="B10" t="n">
-        <v>78645</v>
+        <v>56584</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1598,38 +1598,42 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Bergsvik, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>479790</v>
+        <v>479770</v>
       </c>
       <c r="R10" t="n">
-        <v>6951160</v>
+        <v>6951296</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1656,12 +1660,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2024-08-30</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Uppflog.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1688,10 +1697,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122152031</v>
+        <v>122152142</v>
       </c>
       <c r="B11" t="n">
-        <v>79727</v>
+        <v>78646</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1704,34 +1713,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Brynje, Jmt</t>
+          <t>Bergsvik, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>479817</v>
+        <v>479790</v>
       </c>
       <c r="R11" t="n">
-        <v>6951441</v>
+        <v>6951160</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1758,12 +1767,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1790,10 +1799,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122152042</v>
+        <v>122152024</v>
       </c>
       <c r="B12" t="n">
-        <v>79755</v>
+        <v>79728</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1802,38 +1811,38 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6462</v>
+        <v>2081</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Brynje, Jmt</t>
+          <t>Bergsvik, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>479757</v>
+        <v>479764</v>
       </c>
       <c r="R12" t="n">
-        <v>6951495</v>
+        <v>6951289</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1892,10 +1901,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122152028</v>
+        <v>122152047</v>
       </c>
       <c r="B13" t="n">
-        <v>78645</v>
+        <v>79756</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1904,38 +1913,38 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Bergsvik, Jmt</t>
+          <t>Brynje, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>479733</v>
+        <v>479750</v>
       </c>
       <c r="R13" t="n">
-        <v>6951321</v>
+        <v>6951517</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1994,7 +2003,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122152039</v>
+        <v>122152076</v>
       </c>
       <c r="B14" t="n">
         <v>79727</v>
@@ -2010,34 +2019,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Brynje, Jmt</t>
+          <t>Bergsvik, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>479768</v>
+        <v>479653</v>
       </c>
       <c r="R14" t="n">
-        <v>6951511</v>
+        <v>6951307</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2096,10 +2105,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122152034</v>
+        <v>122152031</v>
       </c>
       <c r="B15" t="n">
-        <v>79726</v>
+        <v>79728</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2112,21 +2121,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2136,10 +2145,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>479844</v>
+        <v>479817</v>
       </c>
       <c r="R15" t="n">
-        <v>6951363</v>
+        <v>6951441</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2198,10 +2207,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122154338</v>
+        <v>122152041</v>
       </c>
       <c r="B16" t="n">
-        <v>79726</v>
+        <v>79727</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2238,10 +2247,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>479524</v>
+        <v>479769</v>
       </c>
       <c r="R16" t="n">
-        <v>6951553</v>
+        <v>6951516</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2268,12 +2277,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-10-05</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-10-05</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2288,22 +2297,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122152033</v>
+        <v>122152055</v>
       </c>
       <c r="B17" t="n">
-        <v>79726</v>
+        <v>90789</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2316,21 +2325,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2340,10 +2349,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>479817</v>
+        <v>479734</v>
       </c>
       <c r="R17" t="n">
-        <v>6951441</v>
+        <v>6951563</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2402,10 +2411,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122152045</v>
+        <v>122152039</v>
       </c>
       <c r="B18" t="n">
-        <v>79726</v>
+        <v>79728</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2418,21 +2427,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2442,10 +2451,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>479758</v>
+        <v>479768</v>
       </c>
       <c r="R18" t="n">
-        <v>6951496</v>
+        <v>6951511</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2504,10 +2513,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122152052</v>
+        <v>122154346</v>
       </c>
       <c r="B19" t="n">
-        <v>79726</v>
+        <v>57527</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2520,21 +2529,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2544,10 +2553,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>479717</v>
+        <v>479569</v>
       </c>
       <c r="R19" t="n">
-        <v>6951549</v>
+        <v>6951576</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2574,12 +2583,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-10-05</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-10-05</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2594,22 +2603,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122152050</v>
+        <v>122152057</v>
       </c>
       <c r="B20" t="n">
-        <v>79727</v>
+        <v>74752</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2622,21 +2631,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2081</v>
+        <v>1467</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2646,10 +2655,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>479716</v>
+        <v>479727</v>
       </c>
       <c r="R20" t="n">
-        <v>6951549</v>
+        <v>6951580</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2682,6 +2691,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2024-08-30</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>På granstubbe intill bäck.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2708,10 +2722,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122152074</v>
+        <v>122152081</v>
       </c>
       <c r="B21" t="n">
-        <v>79727</v>
+        <v>79728</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2748,10 +2762,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>479654</v>
+        <v>479613</v>
       </c>
       <c r="R21" t="n">
-        <v>6951309</v>
+        <v>6951267</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2810,10 +2824,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122152054</v>
+        <v>122152068</v>
       </c>
       <c r="B22" t="n">
-        <v>79726</v>
+        <v>95732</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2826,21 +2840,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>53</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2850,10 +2864,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>479731</v>
+        <v>479630</v>
       </c>
       <c r="R22" t="n">
-        <v>6951554</v>
+        <v>6951446</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2886,6 +2900,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2024-08-30</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>På murken granlåga i gransumpskog.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2912,10 +2931,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122152079</v>
+        <v>122152042</v>
       </c>
       <c r="B23" t="n">
-        <v>79727</v>
+        <v>79756</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2924,38 +2943,38 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2081</v>
+        <v>6462</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Bergsvik, Jmt</t>
+          <t>Brynje, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>479619</v>
+        <v>479757</v>
       </c>
       <c r="R23" t="n">
-        <v>6951287</v>
+        <v>6951495</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3014,10 +3033,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122154345</v>
+        <v>122152049</v>
       </c>
       <c r="B24" t="n">
-        <v>97129</v>
+        <v>79727</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3026,25 +3045,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>221945</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3054,10 +3073,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>479596</v>
+        <v>479749</v>
       </c>
       <c r="R24" t="n">
-        <v>6951595</v>
+        <v>6951522</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3084,12 +3103,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2024-10-05</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2024-10-05</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3104,22 +3123,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122152023</v>
+        <v>122154338</v>
       </c>
       <c r="B25" t="n">
-        <v>56576</v>
+        <v>79727</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3132,38 +3151,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>102612</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Bergsvik, Jmt</t>
+          <t>Brynje, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>479776</v>
+        <v>479524</v>
       </c>
       <c r="R25" t="n">
-        <v>6951285</v>
+        <v>6951553</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3190,12 +3205,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-10-05</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-10-05</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3210,22 +3225,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122152041</v>
+        <v>122152052</v>
       </c>
       <c r="B26" t="n">
-        <v>79726</v>
+        <v>79727</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3262,10 +3277,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>479769</v>
+        <v>479717</v>
       </c>
       <c r="R26" t="n">
-        <v>6951516</v>
+        <v>6951549</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3324,10 +3339,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122152026</v>
+        <v>122152033</v>
       </c>
       <c r="B27" t="n">
-        <v>79726</v>
+        <v>79727</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3360,14 +3375,14 @@
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Bergsvik, Jmt</t>
+          <t>Brynje, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>479764</v>
+        <v>479817</v>
       </c>
       <c r="R27" t="n">
-        <v>6951290</v>
+        <v>6951441</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3426,10 +3441,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122152024</v>
+        <v>122152044</v>
       </c>
       <c r="B28" t="n">
-        <v>79727</v>
+        <v>79728</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3462,14 +3477,14 @@
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Bergsvik, Jmt</t>
+          <t>Brynje, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>479764</v>
+        <v>479757</v>
       </c>
       <c r="R28" t="n">
-        <v>6951289</v>
+        <v>6951495</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3528,10 +3543,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122152047</v>
+        <v>122152073</v>
       </c>
       <c r="B29" t="n">
-        <v>79755</v>
+        <v>79728</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3540,38 +3555,38 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6462</v>
+        <v>2081</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Brynje, Jmt</t>
+          <t>Bergsvik, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>479750</v>
+        <v>479656</v>
       </c>
       <c r="R29" t="n">
-        <v>6951517</v>
+        <v>6951332</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3630,10 +3645,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122152077</v>
+        <v>122152034</v>
       </c>
       <c r="B30" t="n">
-        <v>79726</v>
+        <v>79727</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3666,14 +3681,14 @@
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Bergsvik, Jmt</t>
+          <t>Brynje, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>479619</v>
+        <v>479844</v>
       </c>
       <c r="R30" t="n">
-        <v>6951287</v>
+        <v>6951363</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3732,10 +3747,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122152068</v>
+        <v>122152026</v>
       </c>
       <c r="B31" t="n">
-        <v>95722</v>
+        <v>79727</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3748,34 +3763,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>53</v>
+        <v>6458</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Brynje, Jmt</t>
+          <t>Bergsvik, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>479630</v>
+        <v>479764</v>
       </c>
       <c r="R31" t="n">
-        <v>6951446</v>
+        <v>6951290</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3808,11 +3823,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2024-08-30</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>På murken granlåga i gransumpskog.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3839,10 +3849,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122152071</v>
+        <v>122154343</v>
       </c>
       <c r="B32" t="n">
-        <v>79726</v>
+        <v>94211</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3851,38 +3861,38 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6458</v>
+        <v>2387</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Källpraktmossa</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pseudobryum cinclidioides</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Huebener) T.J.Kop.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Bergsvik, Jmt</t>
+          <t>Brynje, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>479656</v>
+        <v>479547</v>
       </c>
       <c r="R32" t="n">
-        <v>6951332</v>
+        <v>6951577</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -3909,12 +3919,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-10-05</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-10-05</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3929,22 +3939,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122154346</v>
+        <v>122152071</v>
       </c>
       <c r="B33" t="n">
-        <v>57527</v>
+        <v>79727</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3957,34 +3967,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Brynje, Jmt</t>
+          <t>Bergsvik, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>479569</v>
+        <v>479656</v>
       </c>
       <c r="R33" t="n">
-        <v>6951576</v>
+        <v>6951332</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4011,12 +4021,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2024-10-05</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2024-10-05</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4031,22 +4041,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122152029</v>
+        <v>122152023</v>
       </c>
       <c r="B34" t="n">
-        <v>79755</v>
+        <v>56576</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4055,38 +4065,42 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6462</v>
+        <v>102612</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Brynje, Jmt</t>
+          <t>Bergsvik, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>479816</v>
+        <v>479776</v>
       </c>
       <c r="R34" t="n">
-        <v>6951443</v>
+        <v>6951285</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4145,10 +4159,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122152021</v>
+        <v>122152028</v>
       </c>
       <c r="B35" t="n">
-        <v>56584</v>
+        <v>78646</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4157,42 +4171,38 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Bergsvik, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>479770</v>
+        <v>479733</v>
       </c>
       <c r="R35" t="n">
-        <v>6951296</v>
+        <v>6951321</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4225,11 +4235,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2024-08-30</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Uppflog.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4256,10 +4261,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122152049</v>
+        <v>122152064</v>
       </c>
       <c r="B36" t="n">
-        <v>79726</v>
+        <v>98521</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4268,25 +4273,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6458</v>
+        <v>219880</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4296,10 +4301,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>479749</v>
+        <v>479647</v>
       </c>
       <c r="R36" t="n">
-        <v>6951522</v>
+        <v>6951498</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4358,10 +4363,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122152073</v>
+        <v>122152050</v>
       </c>
       <c r="B37" t="n">
-        <v>79727</v>
+        <v>79728</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4394,14 +4399,14 @@
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Bergsvik, Jmt</t>
+          <t>Brynje, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>479656</v>
+        <v>479716</v>
       </c>
       <c r="R37" t="n">
-        <v>6951332</v>
+        <v>6951549</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4460,10 +4465,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122152057</v>
+        <v>122152029</v>
       </c>
       <c r="B38" t="n">
-        <v>74752</v>
+        <v>79756</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4472,25 +4477,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1467</v>
+        <v>6462</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4500,10 +4505,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>479727</v>
+        <v>479816</v>
       </c>
       <c r="R38" t="n">
-        <v>6951580</v>
+        <v>6951443</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4536,11 +4541,6 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2024-08-30</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>På granstubbe intill bäck.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4567,10 +4567,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122152055</v>
+        <v>122154345</v>
       </c>
       <c r="B39" t="n">
-        <v>90779</v>
+        <v>97139</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4579,25 +4579,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1202</v>
+        <v>221945</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4607,10 +4607,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>479734</v>
+        <v>479596</v>
       </c>
       <c r="R39" t="n">
-        <v>6951563</v>
+        <v>6951595</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4637,12 +4637,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-10-05</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-10-05</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4657,19 +4657,19 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122152044</v>
+        <v>122152054</v>
       </c>
       <c r="B40" t="n">
         <v>79727</v>
@@ -4685,21 +4685,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4709,10 +4709,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>479757</v>
+        <v>479731</v>
       </c>
       <c r="R40" t="n">
-        <v>6951495</v>
+        <v>6951554</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4771,10 +4771,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122152064</v>
+        <v>122152079</v>
       </c>
       <c r="B41" t="n">
-        <v>98511</v>
+        <v>79728</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4783,38 +4783,38 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>219880</v>
+        <v>2081</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Brynje, Jmt</t>
+          <t>Bergsvik, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>479647</v>
+        <v>479619</v>
       </c>
       <c r="R41" t="n">
-        <v>6951498</v>
+        <v>6951287</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -4876,7 +4876,7 @@
         <v>122152037</v>
       </c>
       <c r="B42" t="n">
-        <v>79755</v>
+        <v>79756</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>

--- a/artfynd/A 18303-2024 artfynd.xlsx
+++ b/artfynd/A 18303-2024 artfynd.xlsx
@@ -1280,7 +1280,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122152077</v>
+        <v>122152076</v>
       </c>
       <c r="B7" t="n">
         <v>79727</v>
@@ -1320,10 +1320,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>479619</v>
+        <v>479653</v>
       </c>
       <c r="R7" t="n">
-        <v>6951287</v>
+        <v>6951307</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1382,10 +1382,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122152074</v>
+        <v>122152041</v>
       </c>
       <c r="B8" t="n">
-        <v>79728</v>
+        <v>79727</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1398,34 +1398,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Bergsvik, Jmt</t>
+          <t>Brynje, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>479654</v>
+        <v>479769</v>
       </c>
       <c r="R8" t="n">
-        <v>6951309</v>
+        <v>6951516</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1484,10 +1484,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122152045</v>
+        <v>122152028</v>
       </c>
       <c r="B9" t="n">
-        <v>79727</v>
+        <v>78646</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1500,34 +1500,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Brynje, Jmt</t>
+          <t>Bergsvik, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>479758</v>
+        <v>479733</v>
       </c>
       <c r="R9" t="n">
-        <v>6951496</v>
+        <v>6951321</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1586,10 +1586,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122152021</v>
+        <v>122152071</v>
       </c>
       <c r="B10" t="n">
-        <v>56584</v>
+        <v>79727</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1598,42 +1598,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100138</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Bergsvik, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>479770</v>
+        <v>479656</v>
       </c>
       <c r="R10" t="n">
-        <v>6951296</v>
+        <v>6951332</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1666,11 +1662,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-08-30</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Uppflog.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1697,10 +1688,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122152142</v>
+        <v>122152033</v>
       </c>
       <c r="B11" t="n">
-        <v>78646</v>
+        <v>79727</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1713,34 +1704,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Bergsvik, Jmt</t>
+          <t>Brynje, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>479790</v>
+        <v>479817</v>
       </c>
       <c r="R11" t="n">
-        <v>6951160</v>
+        <v>6951441</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1767,12 +1758,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1799,10 +1790,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122152024</v>
+        <v>122152045</v>
       </c>
       <c r="B12" t="n">
-        <v>79728</v>
+        <v>79727</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1815,34 +1806,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Bergsvik, Jmt</t>
+          <t>Brynje, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>479764</v>
+        <v>479758</v>
       </c>
       <c r="R12" t="n">
-        <v>6951289</v>
+        <v>6951496</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1901,10 +1892,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122152047</v>
+        <v>122154345</v>
       </c>
       <c r="B13" t="n">
-        <v>79756</v>
+        <v>97139</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1917,21 +1908,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6462</v>
+        <v>221945</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1941,10 +1932,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>479750</v>
+        <v>479596</v>
       </c>
       <c r="R13" t="n">
-        <v>6951517</v>
+        <v>6951595</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1971,12 +1962,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-10-05</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-10-05</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1991,19 +1982,19 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122152076</v>
+        <v>122152077</v>
       </c>
       <c r="B14" t="n">
         <v>79727</v>
@@ -2043,10 +2034,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>479653</v>
+        <v>479619</v>
       </c>
       <c r="R14" t="n">
-        <v>6951307</v>
+        <v>6951287</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2105,10 +2096,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122152031</v>
+        <v>122152023</v>
       </c>
       <c r="B15" t="n">
-        <v>79728</v>
+        <v>56576</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2121,34 +2112,38 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2081</v>
+        <v>102612</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Brynje, Jmt</t>
+          <t>Bergsvik, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>479817</v>
+        <v>479776</v>
       </c>
       <c r="R15" t="n">
-        <v>6951441</v>
+        <v>6951285</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2207,10 +2202,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122152041</v>
+        <v>122152021</v>
       </c>
       <c r="B16" t="n">
-        <v>79727</v>
+        <v>56584</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2219,38 +2214,42 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>100138</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Brynje, Jmt</t>
+          <t>Bergsvik, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>479769</v>
+        <v>479770</v>
       </c>
       <c r="R16" t="n">
-        <v>6951516</v>
+        <v>6951296</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2283,6 +2282,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2024-08-30</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Uppflog.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2309,10 +2313,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122152055</v>
+        <v>122154346</v>
       </c>
       <c r="B17" t="n">
-        <v>90789</v>
+        <v>57527</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2325,21 +2329,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2349,10 +2353,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>479734</v>
+        <v>479569</v>
       </c>
       <c r="R17" t="n">
-        <v>6951563</v>
+        <v>6951576</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2379,12 +2383,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-10-05</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-10-05</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2399,19 +2403,19 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122152039</v>
+        <v>122152031</v>
       </c>
       <c r="B18" t="n">
         <v>79728</v>
@@ -2451,10 +2455,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>479768</v>
+        <v>479817</v>
       </c>
       <c r="R18" t="n">
-        <v>6951511</v>
+        <v>6951441</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2513,10 +2517,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122154346</v>
+        <v>122152073</v>
       </c>
       <c r="B19" t="n">
-        <v>57527</v>
+        <v>79728</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2529,34 +2533,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>103021</v>
+        <v>2081</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Brynje, Jmt</t>
+          <t>Bergsvik, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>479569</v>
+        <v>479656</v>
       </c>
       <c r="R19" t="n">
-        <v>6951576</v>
+        <v>6951332</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2583,12 +2587,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2024-10-05</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2024-10-05</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2603,22 +2607,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122152057</v>
+        <v>122152052</v>
       </c>
       <c r="B20" t="n">
-        <v>74752</v>
+        <v>79727</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2631,21 +2635,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1467</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2655,10 +2659,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>479727</v>
+        <v>479717</v>
       </c>
       <c r="R20" t="n">
-        <v>6951580</v>
+        <v>6951549</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2691,11 +2695,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2024-08-30</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>På granstubbe intill bäck.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2722,10 +2721,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122152081</v>
+        <v>122152068</v>
       </c>
       <c r="B21" t="n">
-        <v>79728</v>
+        <v>95732</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2738,34 +2737,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2081</v>
+        <v>53</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Bergsvik, Jmt</t>
+          <t>Brynje, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>479613</v>
+        <v>479630</v>
       </c>
       <c r="R21" t="n">
-        <v>6951267</v>
+        <v>6951446</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2798,6 +2797,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2024-08-30</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>På murken granlåga i gransumpskog.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2824,10 +2828,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122152068</v>
+        <v>122152079</v>
       </c>
       <c r="B22" t="n">
-        <v>95732</v>
+        <v>79728</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2840,34 +2844,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>53</v>
+        <v>2081</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Brynje, Jmt</t>
+          <t>Bergsvik, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>479630</v>
+        <v>479619</v>
       </c>
       <c r="R22" t="n">
-        <v>6951446</v>
+        <v>6951287</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2900,11 +2904,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2024-08-30</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>På murken granlåga i gransumpskog.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2931,10 +2930,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122152042</v>
+        <v>122154343</v>
       </c>
       <c r="B23" t="n">
-        <v>79756</v>
+        <v>94211</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2947,21 +2946,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6462</v>
+        <v>2387</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Källpraktmossa</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Pseudobryum cinclidioides</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Huebener) T.J.Kop.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2971,10 +2970,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>479757</v>
+        <v>479547</v>
       </c>
       <c r="R23" t="n">
-        <v>6951495</v>
+        <v>6951577</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3001,12 +3000,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-10-05</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-10-05</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3021,22 +3020,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122152049</v>
+        <v>122152037</v>
       </c>
       <c r="B24" t="n">
-        <v>79727</v>
+        <v>79756</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3045,25 +3044,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3073,10 +3072,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>479749</v>
+        <v>479767</v>
       </c>
       <c r="R24" t="n">
-        <v>6951522</v>
+        <v>6951509</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3135,10 +3134,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122154338</v>
+        <v>122152047</v>
       </c>
       <c r="B25" t="n">
-        <v>79727</v>
+        <v>79756</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3147,25 +3146,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3175,10 +3174,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>479524</v>
+        <v>479750</v>
       </c>
       <c r="R25" t="n">
-        <v>6951553</v>
+        <v>6951517</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3205,12 +3204,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2024-10-05</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2024-10-05</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3225,22 +3224,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122152052</v>
+        <v>122152042</v>
       </c>
       <c r="B26" t="n">
-        <v>79727</v>
+        <v>79756</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3249,25 +3248,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3277,10 +3276,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>479717</v>
+        <v>479757</v>
       </c>
       <c r="R26" t="n">
-        <v>6951549</v>
+        <v>6951495</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3339,10 +3338,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122152033</v>
+        <v>122152044</v>
       </c>
       <c r="B27" t="n">
-        <v>79727</v>
+        <v>79728</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3355,21 +3354,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3379,10 +3378,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>479817</v>
+        <v>479757</v>
       </c>
       <c r="R27" t="n">
-        <v>6951441</v>
+        <v>6951495</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3441,10 +3440,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122152044</v>
+        <v>122152055</v>
       </c>
       <c r="B28" t="n">
-        <v>79728</v>
+        <v>90789</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3457,21 +3456,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2081</v>
+        <v>1202</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3481,10 +3480,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>479757</v>
+        <v>479734</v>
       </c>
       <c r="R28" t="n">
-        <v>6951495</v>
+        <v>6951563</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3543,10 +3542,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122152073</v>
+        <v>122154338</v>
       </c>
       <c r="B29" t="n">
-        <v>79728</v>
+        <v>79727</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3559,34 +3558,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Bergsvik, Jmt</t>
+          <t>Brynje, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>479656</v>
+        <v>479524</v>
       </c>
       <c r="R29" t="n">
-        <v>6951332</v>
+        <v>6951553</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3613,12 +3612,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-10-05</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-10-05</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3633,22 +3632,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122152034</v>
+        <v>122152029</v>
       </c>
       <c r="B30" t="n">
-        <v>79727</v>
+        <v>79756</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3657,25 +3656,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3685,10 +3684,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>479844</v>
+        <v>479816</v>
       </c>
       <c r="R30" t="n">
-        <v>6951363</v>
+        <v>6951443</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3747,7 +3746,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122152026</v>
+        <v>122152034</v>
       </c>
       <c r="B31" t="n">
         <v>79727</v>
@@ -3783,14 +3782,14 @@
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Bergsvik, Jmt</t>
+          <t>Brynje, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>479764</v>
+        <v>479844</v>
       </c>
       <c r="R31" t="n">
-        <v>6951290</v>
+        <v>6951363</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3849,10 +3848,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122154343</v>
+        <v>122152026</v>
       </c>
       <c r="B32" t="n">
-        <v>94211</v>
+        <v>79727</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3861,38 +3860,38 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>2387</v>
+        <v>6458</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Källpraktmossa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Pseudobryum cinclidioides</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Huebener) T.J.Kop.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Brynje, Jmt</t>
+          <t>Bergsvik, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>479547</v>
+        <v>479764</v>
       </c>
       <c r="R32" t="n">
-        <v>6951577</v>
+        <v>6951290</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -3919,12 +3918,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2024-10-05</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2024-10-05</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3939,22 +3938,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122152071</v>
+        <v>122152050</v>
       </c>
       <c r="B33" t="n">
-        <v>79727</v>
+        <v>79728</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3967,34 +3966,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Bergsvik, Jmt</t>
+          <t>Brynje, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>479656</v>
+        <v>479716</v>
       </c>
       <c r="R33" t="n">
-        <v>6951332</v>
+        <v>6951549</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4053,10 +4052,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122152023</v>
+        <v>122152039</v>
       </c>
       <c r="B34" t="n">
-        <v>56576</v>
+        <v>79728</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4069,38 +4068,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>102612</v>
+        <v>2081</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Bergsvik, Jmt</t>
+          <t>Brynje, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>479776</v>
+        <v>479768</v>
       </c>
       <c r="R34" t="n">
-        <v>6951285</v>
+        <v>6951511</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4159,10 +4154,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122152028</v>
+        <v>122152024</v>
       </c>
       <c r="B35" t="n">
-        <v>78646</v>
+        <v>79728</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4175,21 +4170,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4199,10 +4194,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>479733</v>
+        <v>479764</v>
       </c>
       <c r="R35" t="n">
-        <v>6951321</v>
+        <v>6951289</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4261,10 +4256,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122152064</v>
+        <v>122152057</v>
       </c>
       <c r="B36" t="n">
-        <v>98521</v>
+        <v>74752</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4273,25 +4268,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>219880</v>
+        <v>1467</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4301,10 +4296,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>479647</v>
+        <v>479727</v>
       </c>
       <c r="R36" t="n">
-        <v>6951498</v>
+        <v>6951580</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4337,6 +4332,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2024-08-30</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>På granstubbe intill bäck.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4363,7 +4363,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122152050</v>
+        <v>122152081</v>
       </c>
       <c r="B37" t="n">
         <v>79728</v>
@@ -4399,14 +4399,14 @@
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Brynje, Jmt</t>
+          <t>Bergsvik, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>479716</v>
+        <v>479613</v>
       </c>
       <c r="R37" t="n">
-        <v>6951549</v>
+        <v>6951267</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4465,10 +4465,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122152029</v>
+        <v>122152142</v>
       </c>
       <c r="B38" t="n">
-        <v>79756</v>
+        <v>78646</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4477,38 +4477,38 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Brynje, Jmt</t>
+          <t>Bergsvik, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>479816</v>
+        <v>479790</v>
       </c>
       <c r="R38" t="n">
-        <v>6951443</v>
+        <v>6951160</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4535,12 +4535,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4567,10 +4567,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122154345</v>
+        <v>122152064</v>
       </c>
       <c r="B39" t="n">
-        <v>97139</v>
+        <v>98521</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4583,21 +4583,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>221945</v>
+        <v>219880</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4607,10 +4607,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>479596</v>
+        <v>479647</v>
       </c>
       <c r="R39" t="n">
-        <v>6951595</v>
+        <v>6951498</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4637,12 +4637,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2024-10-05</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2024-10-05</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4657,19 +4657,19 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122152054</v>
+        <v>122152049</v>
       </c>
       <c r="B40" t="n">
         <v>79727</v>
@@ -4709,10 +4709,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>479731</v>
+        <v>479749</v>
       </c>
       <c r="R40" t="n">
-        <v>6951554</v>
+        <v>6951522</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4771,7 +4771,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122152079</v>
+        <v>122152074</v>
       </c>
       <c r="B41" t="n">
         <v>79728</v>
@@ -4811,10 +4811,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>479619</v>
+        <v>479654</v>
       </c>
       <c r="R41" t="n">
-        <v>6951287</v>
+        <v>6951309</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -4873,10 +4873,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122152037</v>
+        <v>122152054</v>
       </c>
       <c r="B42" t="n">
-        <v>79756</v>
+        <v>79727</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4885,25 +4885,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4913,10 +4913,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>479767</v>
+        <v>479731</v>
       </c>
       <c r="R42" t="n">
-        <v>6951509</v>
+        <v>6951554</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>

--- a/artfynd/A 18303-2024 artfynd.xlsx
+++ b/artfynd/A 18303-2024 artfynd.xlsx
@@ -1688,7 +1688,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122152033</v>
+        <v>122152045</v>
       </c>
       <c r="B11" t="n">
         <v>79727</v>
@@ -1728,10 +1728,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>479817</v>
+        <v>479758</v>
       </c>
       <c r="R11" t="n">
-        <v>6951441</v>
+        <v>6951496</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1790,7 +1790,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122152045</v>
+        <v>122152033</v>
       </c>
       <c r="B12" t="n">
         <v>79727</v>
@@ -1830,10 +1830,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>479758</v>
+        <v>479817</v>
       </c>
       <c r="R12" t="n">
-        <v>6951496</v>
+        <v>6951441</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -4052,10 +4052,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122152039</v>
+        <v>122152142</v>
       </c>
       <c r="B34" t="n">
-        <v>79728</v>
+        <v>78646</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4068,34 +4068,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Brynje, Jmt</t>
+          <t>Bergsvik, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>479768</v>
+        <v>479790</v>
       </c>
       <c r="R34" t="n">
-        <v>6951511</v>
+        <v>6951160</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4122,12 +4122,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4154,7 +4154,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122152024</v>
+        <v>122152039</v>
       </c>
       <c r="B35" t="n">
         <v>79728</v>
@@ -4190,14 +4190,14 @@
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Bergsvik, Jmt</t>
+          <t>Brynje, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>479764</v>
+        <v>479768</v>
       </c>
       <c r="R35" t="n">
-        <v>6951289</v>
+        <v>6951511</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4256,10 +4256,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122152057</v>
+        <v>122152024</v>
       </c>
       <c r="B36" t="n">
-        <v>74752</v>
+        <v>79728</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4272,34 +4272,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1467</v>
+        <v>2081</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Brynje, Jmt</t>
+          <t>Bergsvik, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>479727</v>
+        <v>479764</v>
       </c>
       <c r="R36" t="n">
-        <v>6951580</v>
+        <v>6951289</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4332,11 +4332,6 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2024-08-30</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>På granstubbe intill bäck.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4363,10 +4358,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122152081</v>
+        <v>122152057</v>
       </c>
       <c r="B37" t="n">
-        <v>79728</v>
+        <v>74752</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4379,34 +4374,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>2081</v>
+        <v>1467</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Bergsvik, Jmt</t>
+          <t>Brynje, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>479613</v>
+        <v>479727</v>
       </c>
       <c r="R37" t="n">
-        <v>6951267</v>
+        <v>6951580</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4439,6 +4434,11 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2024-08-30</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>På granstubbe intill bäck.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4465,10 +4465,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122152142</v>
+        <v>122152081</v>
       </c>
       <c r="B38" t="n">
-        <v>78646</v>
+        <v>79728</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4481,21 +4481,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4505,10 +4505,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>479790</v>
+        <v>479613</v>
       </c>
       <c r="R38" t="n">
-        <v>6951160</v>
+        <v>6951267</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4535,12 +4535,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4567,10 +4567,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122152064</v>
+        <v>122152049</v>
       </c>
       <c r="B39" t="n">
-        <v>98521</v>
+        <v>79727</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4579,25 +4579,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>219880</v>
+        <v>6458</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4607,10 +4607,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>479647</v>
+        <v>479749</v>
       </c>
       <c r="R39" t="n">
-        <v>6951498</v>
+        <v>6951522</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4669,10 +4669,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122152049</v>
+        <v>122152064</v>
       </c>
       <c r="B40" t="n">
-        <v>79727</v>
+        <v>98521</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4681,25 +4681,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6458</v>
+        <v>219880</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4709,10 +4709,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>479749</v>
+        <v>479647</v>
       </c>
       <c r="R40" t="n">
-        <v>6951522</v>
+        <v>6951498</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>

--- a/artfynd/A 18303-2024 artfynd.xlsx
+++ b/artfynd/A 18303-2024 artfynd.xlsx
@@ -1280,10 +1280,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122152076</v>
+        <v>122152142</v>
       </c>
       <c r="B7" t="n">
-        <v>79727</v>
+        <v>78651</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1296,21 +1296,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1320,10 +1320,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>479653</v>
+        <v>479790</v>
       </c>
       <c r="R7" t="n">
-        <v>6951307</v>
+        <v>6951160</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1350,12 +1350,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1385,7 +1385,7 @@
         <v>122152041</v>
       </c>
       <c r="B8" t="n">
-        <v>79727</v>
+        <v>79732</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1484,10 +1484,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122152028</v>
+        <v>122152050</v>
       </c>
       <c r="B9" t="n">
-        <v>78646</v>
+        <v>79733</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1500,34 +1500,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Bergsvik, Jmt</t>
+          <t>Brynje, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>479733</v>
+        <v>479716</v>
       </c>
       <c r="R9" t="n">
-        <v>6951321</v>
+        <v>6951549</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1586,10 +1586,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122152071</v>
+        <v>122152049</v>
       </c>
       <c r="B10" t="n">
-        <v>79727</v>
+        <v>79732</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1622,14 +1622,14 @@
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Bergsvik, Jmt</t>
+          <t>Brynje, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>479656</v>
+        <v>479749</v>
       </c>
       <c r="R10" t="n">
-        <v>6951332</v>
+        <v>6951522</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1688,10 +1688,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122152045</v>
+        <v>122152033</v>
       </c>
       <c r="B11" t="n">
-        <v>79727</v>
+        <v>79732</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1728,10 +1728,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>479758</v>
+        <v>479817</v>
       </c>
       <c r="R11" t="n">
-        <v>6951496</v>
+        <v>6951441</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1790,10 +1790,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122152033</v>
+        <v>122152037</v>
       </c>
       <c r="B12" t="n">
-        <v>79727</v>
+        <v>79761</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1802,25 +1802,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1830,10 +1830,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>479817</v>
+        <v>479767</v>
       </c>
       <c r="R12" t="n">
-        <v>6951441</v>
+        <v>6951509</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1892,10 +1892,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122154345</v>
+        <v>122152077</v>
       </c>
       <c r="B13" t="n">
-        <v>97139</v>
+        <v>79732</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1904,38 +1904,38 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221945</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Brynje, Jmt</t>
+          <t>Bergsvik, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>479596</v>
+        <v>479619</v>
       </c>
       <c r="R13" t="n">
-        <v>6951595</v>
+        <v>6951287</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1962,12 +1962,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2024-10-05</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2024-10-05</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1982,22 +1982,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122152077</v>
+        <v>122152024</v>
       </c>
       <c r="B14" t="n">
-        <v>79727</v>
+        <v>79733</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2010,21 +2010,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2034,10 +2034,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>479619</v>
+        <v>479764</v>
       </c>
       <c r="R14" t="n">
-        <v>6951287</v>
+        <v>6951289</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2096,10 +2096,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122152023</v>
+        <v>122152076</v>
       </c>
       <c r="B15" t="n">
-        <v>56576</v>
+        <v>79732</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2112,38 +2112,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>102612</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Bergsvik, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>479776</v>
+        <v>479653</v>
       </c>
       <c r="R15" t="n">
-        <v>6951285</v>
+        <v>6951307</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2202,10 +2198,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122152021</v>
+        <v>122152026</v>
       </c>
       <c r="B16" t="n">
-        <v>56584</v>
+        <v>79732</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2214,42 +2210,38 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100138</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Bergsvik, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>479770</v>
+        <v>479764</v>
       </c>
       <c r="R16" t="n">
-        <v>6951296</v>
+        <v>6951290</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2282,11 +2274,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2024-08-30</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Uppflog.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2313,10 +2300,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122154346</v>
+        <v>122152055</v>
       </c>
       <c r="B17" t="n">
-        <v>57527</v>
+        <v>90801</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2329,21 +2316,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2353,10 +2340,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>479569</v>
+        <v>479734</v>
       </c>
       <c r="R17" t="n">
-        <v>6951576</v>
+        <v>6951563</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2383,12 +2370,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2024-10-05</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2024-10-05</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2403,22 +2390,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122152031</v>
+        <v>122152071</v>
       </c>
       <c r="B18" t="n">
-        <v>79728</v>
+        <v>79732</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2431,34 +2418,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Brynje, Jmt</t>
+          <t>Bergsvik, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>479817</v>
+        <v>479656</v>
       </c>
       <c r="R18" t="n">
-        <v>6951441</v>
+        <v>6951332</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2517,10 +2504,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122152073</v>
+        <v>122154338</v>
       </c>
       <c r="B19" t="n">
-        <v>79728</v>
+        <v>79732</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2533,34 +2520,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Bergsvik, Jmt</t>
+          <t>Brynje, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>479656</v>
+        <v>479524</v>
       </c>
       <c r="R19" t="n">
-        <v>6951332</v>
+        <v>6951553</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2587,12 +2574,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-10-05</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-10-05</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2607,12 +2594,12 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
@@ -2622,7 +2609,7 @@
         <v>122152052</v>
       </c>
       <c r="B20" t="n">
-        <v>79727</v>
+        <v>79732</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2721,10 +2708,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122152068</v>
+        <v>122152081</v>
       </c>
       <c r="B21" t="n">
-        <v>95732</v>
+        <v>79733</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2737,34 +2724,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>53</v>
+        <v>2081</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Brynje, Jmt</t>
+          <t>Bergsvik, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>479630</v>
+        <v>479613</v>
       </c>
       <c r="R21" t="n">
-        <v>6951446</v>
+        <v>6951267</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2797,11 +2784,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2024-08-30</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>På murken granlåga i gransumpskog.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2828,10 +2810,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122152079</v>
+        <v>122152042</v>
       </c>
       <c r="B22" t="n">
-        <v>79728</v>
+        <v>79761</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2840,38 +2822,38 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2081</v>
+        <v>6462</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Bergsvik, Jmt</t>
+          <t>Brynje, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>479619</v>
+        <v>479757</v>
       </c>
       <c r="R22" t="n">
-        <v>6951287</v>
+        <v>6951495</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2930,10 +2912,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122154343</v>
+        <v>122152057</v>
       </c>
       <c r="B23" t="n">
-        <v>94211</v>
+        <v>74757</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2942,25 +2924,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2387</v>
+        <v>1467</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Källpraktmossa</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Pseudobryum cinclidioides</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Huebener) T.J.Kop.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2970,10 +2952,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>479547</v>
+        <v>479727</v>
       </c>
       <c r="R23" t="n">
-        <v>6951577</v>
+        <v>6951580</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3000,12 +2982,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2024-10-05</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2024-10-05</t>
+          <t>2024-08-30</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>På granstubbe intill bäck.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3020,22 +3007,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122152037</v>
+        <v>122152034</v>
       </c>
       <c r="B24" t="n">
-        <v>79756</v>
+        <v>79732</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3044,25 +3031,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3072,10 +3059,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>479767</v>
+        <v>479844</v>
       </c>
       <c r="R24" t="n">
-        <v>6951509</v>
+        <v>6951363</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3134,10 +3121,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122152047</v>
+        <v>122152039</v>
       </c>
       <c r="B25" t="n">
-        <v>79756</v>
+        <v>79733</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3146,25 +3133,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6462</v>
+        <v>2081</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3174,10 +3161,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>479750</v>
+        <v>479768</v>
       </c>
       <c r="R25" t="n">
-        <v>6951517</v>
+        <v>6951511</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3236,10 +3223,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122152042</v>
+        <v>122152021</v>
       </c>
       <c r="B26" t="n">
-        <v>79756</v>
+        <v>56589</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3252,34 +3239,38 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6462</v>
+        <v>100138</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Brynje, Jmt</t>
+          <t>Bergsvik, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>479757</v>
+        <v>479770</v>
       </c>
       <c r="R26" t="n">
-        <v>6951495</v>
+        <v>6951296</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3312,6 +3303,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2024-08-30</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Uppflog.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3338,10 +3334,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122152044</v>
+        <v>122154346</v>
       </c>
       <c r="B27" t="n">
-        <v>79728</v>
+        <v>57532</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3354,21 +3350,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2081</v>
+        <v>103021</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3378,10 +3374,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>479757</v>
+        <v>479569</v>
       </c>
       <c r="R27" t="n">
-        <v>6951495</v>
+        <v>6951576</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3408,12 +3404,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-10-05</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-10-05</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3428,22 +3424,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122152055</v>
+        <v>122154345</v>
       </c>
       <c r="B28" t="n">
-        <v>90789</v>
+        <v>97151</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3452,25 +3448,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1202</v>
+        <v>221945</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3480,10 +3476,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>479734</v>
+        <v>479596</v>
       </c>
       <c r="R28" t="n">
-        <v>6951563</v>
+        <v>6951595</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3510,12 +3506,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-10-05</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-10-05</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3530,22 +3526,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122154338</v>
+        <v>122152079</v>
       </c>
       <c r="B29" t="n">
-        <v>79727</v>
+        <v>79733</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3558,34 +3554,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Brynje, Jmt</t>
+          <t>Bergsvik, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>479524</v>
+        <v>479619</v>
       </c>
       <c r="R29" t="n">
-        <v>6951553</v>
+        <v>6951287</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3612,12 +3608,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2024-10-05</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2024-10-05</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3632,22 +3628,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122152029</v>
+        <v>122152031</v>
       </c>
       <c r="B30" t="n">
-        <v>79756</v>
+        <v>79733</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3656,25 +3652,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6462</v>
+        <v>2081</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3684,10 +3680,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>479816</v>
+        <v>479817</v>
       </c>
       <c r="R30" t="n">
-        <v>6951443</v>
+        <v>6951441</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3746,10 +3742,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122152034</v>
+        <v>122152045</v>
       </c>
       <c r="B31" t="n">
-        <v>79727</v>
+        <v>79732</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3786,10 +3782,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>479844</v>
+        <v>479758</v>
       </c>
       <c r="R31" t="n">
-        <v>6951363</v>
+        <v>6951496</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3848,10 +3844,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122152026</v>
+        <v>122154343</v>
       </c>
       <c r="B32" t="n">
-        <v>79727</v>
+        <v>94223</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3860,38 +3856,38 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6458</v>
+        <v>2387</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Källpraktmossa</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pseudobryum cinclidioides</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Huebener) T.J.Kop.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Bergsvik, Jmt</t>
+          <t>Brynje, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>479764</v>
+        <v>479547</v>
       </c>
       <c r="R32" t="n">
-        <v>6951290</v>
+        <v>6951577</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -3918,12 +3914,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-10-05</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-10-05</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3938,22 +3934,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122152050</v>
+        <v>122152074</v>
       </c>
       <c r="B33" t="n">
-        <v>79728</v>
+        <v>79733</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3986,14 +3982,14 @@
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Brynje, Jmt</t>
+          <t>Bergsvik, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>479716</v>
+        <v>479654</v>
       </c>
       <c r="R33" t="n">
-        <v>6951549</v>
+        <v>6951309</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4052,10 +4048,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122152142</v>
+        <v>122152028</v>
       </c>
       <c r="B34" t="n">
-        <v>78646</v>
+        <v>78651</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4092,10 +4088,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>479790</v>
+        <v>479733</v>
       </c>
       <c r="R34" t="n">
-        <v>6951160</v>
+        <v>6951321</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4122,12 +4118,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4154,10 +4150,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122152039</v>
+        <v>122152068</v>
       </c>
       <c r="B35" t="n">
-        <v>79728</v>
+        <v>95744</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4170,21 +4166,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>2081</v>
+        <v>53</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4194,10 +4190,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>479768</v>
+        <v>479630</v>
       </c>
       <c r="R35" t="n">
-        <v>6951511</v>
+        <v>6951446</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4230,6 +4226,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2024-08-30</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>På murken granlåga i gransumpskog.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4256,10 +4257,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122152024</v>
+        <v>122152044</v>
       </c>
       <c r="B36" t="n">
-        <v>79728</v>
+        <v>79733</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4292,14 +4293,14 @@
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Bergsvik, Jmt</t>
+          <t>Brynje, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>479764</v>
+        <v>479757</v>
       </c>
       <c r="R36" t="n">
-        <v>6951289</v>
+        <v>6951495</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4358,10 +4359,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122152057</v>
+        <v>122152047</v>
       </c>
       <c r="B37" t="n">
-        <v>74752</v>
+        <v>79761</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4370,25 +4371,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1467</v>
+        <v>6462</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4398,10 +4399,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>479727</v>
+        <v>479750</v>
       </c>
       <c r="R37" t="n">
-        <v>6951580</v>
+        <v>6951517</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4434,11 +4435,6 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2024-08-30</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>På granstubbe intill bäck.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4465,10 +4461,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122152081</v>
+        <v>122152064</v>
       </c>
       <c r="B38" t="n">
-        <v>79728</v>
+        <v>98533</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4477,38 +4473,38 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>2081</v>
+        <v>219880</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Bergsvik, Jmt</t>
+          <t>Brynje, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>479613</v>
+        <v>479647</v>
       </c>
       <c r="R38" t="n">
-        <v>6951267</v>
+        <v>6951498</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4567,10 +4563,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122152049</v>
+        <v>122152073</v>
       </c>
       <c r="B39" t="n">
-        <v>79727</v>
+        <v>79733</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4583,34 +4579,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Brynje, Jmt</t>
+          <t>Bergsvik, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>479749</v>
+        <v>479656</v>
       </c>
       <c r="R39" t="n">
-        <v>6951522</v>
+        <v>6951332</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4669,10 +4665,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122152064</v>
+        <v>122152023</v>
       </c>
       <c r="B40" t="n">
-        <v>98521</v>
+        <v>56581</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4681,38 +4677,42 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>219880</v>
+        <v>102612</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Brynje, Jmt</t>
+          <t>Bergsvik, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>479647</v>
+        <v>479776</v>
       </c>
       <c r="R40" t="n">
-        <v>6951498</v>
+        <v>6951285</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4771,10 +4771,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122152074</v>
+        <v>122152029</v>
       </c>
       <c r="B41" t="n">
-        <v>79728</v>
+        <v>79761</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4783,38 +4783,38 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>2081</v>
+        <v>6462</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Bergsvik, Jmt</t>
+          <t>Brynje, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>479654</v>
+        <v>479816</v>
       </c>
       <c r="R41" t="n">
-        <v>6951309</v>
+        <v>6951443</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -4876,7 +4876,7 @@
         <v>122152054</v>
       </c>
       <c r="B42" t="n">
-        <v>79727</v>
+        <v>79732</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>

--- a/artfynd/A 18303-2024 artfynd.xlsx
+++ b/artfynd/A 18303-2024 artfynd.xlsx
@@ -1382,7 +1382,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122152041</v>
+        <v>122152071</v>
       </c>
       <c r="B8" t="n">
         <v>79732</v>
@@ -1418,14 +1418,14 @@
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Brynje, Jmt</t>
+          <t>Bergsvik, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>479769</v>
+        <v>479656</v>
       </c>
       <c r="R8" t="n">
-        <v>6951516</v>
+        <v>6951332</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1484,7 +1484,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122152050</v>
+        <v>122152074</v>
       </c>
       <c r="B9" t="n">
         <v>79733</v>
@@ -1520,14 +1520,14 @@
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Brynje, Jmt</t>
+          <t>Bergsvik, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>479716</v>
+        <v>479654</v>
       </c>
       <c r="R9" t="n">
-        <v>6951549</v>
+        <v>6951309</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1586,7 +1586,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122152049</v>
+        <v>122152077</v>
       </c>
       <c r="B10" t="n">
         <v>79732</v>
@@ -1622,14 +1622,14 @@
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Brynje, Jmt</t>
+          <t>Bergsvik, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>479749</v>
+        <v>479619</v>
       </c>
       <c r="R10" t="n">
-        <v>6951522</v>
+        <v>6951287</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1688,10 +1688,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122152033</v>
+        <v>122154345</v>
       </c>
       <c r="B11" t="n">
-        <v>79732</v>
+        <v>97156</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1700,25 +1700,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>221945</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1728,10 +1728,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>479817</v>
+        <v>479596</v>
       </c>
       <c r="R11" t="n">
-        <v>6951441</v>
+        <v>6951595</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1758,12 +1758,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-10-05</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-10-05</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1778,22 +1778,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122152037</v>
+        <v>122152055</v>
       </c>
       <c r="B12" t="n">
-        <v>79761</v>
+        <v>90808</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1802,25 +1802,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6462</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1830,10 +1830,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>479767</v>
+        <v>479734</v>
       </c>
       <c r="R12" t="n">
-        <v>6951509</v>
+        <v>6951563</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1892,10 +1892,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122152077</v>
+        <v>122152037</v>
       </c>
       <c r="B13" t="n">
-        <v>79732</v>
+        <v>79761</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1904,38 +1904,38 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Bergsvik, Jmt</t>
+          <t>Brynje, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>479619</v>
+        <v>479767</v>
       </c>
       <c r="R13" t="n">
-        <v>6951287</v>
+        <v>6951509</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2096,7 +2096,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122152076</v>
+        <v>122152054</v>
       </c>
       <c r="B15" t="n">
         <v>79732</v>
@@ -2132,14 +2132,14 @@
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Bergsvik, Jmt</t>
+          <t>Brynje, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>479653</v>
+        <v>479731</v>
       </c>
       <c r="R15" t="n">
-        <v>6951307</v>
+        <v>6951554</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2198,10 +2198,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122152026</v>
+        <v>122152057</v>
       </c>
       <c r="B16" t="n">
-        <v>79732</v>
+        <v>74757</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2214,34 +2214,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>1467</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Bergsvik, Jmt</t>
+          <t>Brynje, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>479764</v>
+        <v>479727</v>
       </c>
       <c r="R16" t="n">
-        <v>6951290</v>
+        <v>6951580</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2274,6 +2274,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2024-08-30</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>På granstubbe intill bäck.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2300,10 +2305,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122152055</v>
+        <v>122152026</v>
       </c>
       <c r="B17" t="n">
-        <v>90801</v>
+        <v>79732</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2316,34 +2321,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Brynje, Jmt</t>
+          <t>Bergsvik, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>479734</v>
+        <v>479764</v>
       </c>
       <c r="R17" t="n">
-        <v>6951563</v>
+        <v>6951290</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2402,10 +2407,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122152071</v>
+        <v>122152081</v>
       </c>
       <c r="B18" t="n">
-        <v>79732</v>
+        <v>79733</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2418,21 +2423,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2442,10 +2447,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>479656</v>
+        <v>479613</v>
       </c>
       <c r="R18" t="n">
-        <v>6951332</v>
+        <v>6951267</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2504,10 +2509,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122154338</v>
+        <v>122152023</v>
       </c>
       <c r="B19" t="n">
-        <v>79732</v>
+        <v>56581</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2520,34 +2525,38 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>102612</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Brynje, Jmt</t>
+          <t>Bergsvik, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>479524</v>
+        <v>479776</v>
       </c>
       <c r="R19" t="n">
-        <v>6951553</v>
+        <v>6951285</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2574,12 +2583,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2024-10-05</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2024-10-05</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2594,22 +2603,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122152052</v>
+        <v>122152044</v>
       </c>
       <c r="B20" t="n">
-        <v>79732</v>
+        <v>79733</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2622,21 +2631,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2646,10 +2655,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>479717</v>
+        <v>479757</v>
       </c>
       <c r="R20" t="n">
-        <v>6951549</v>
+        <v>6951495</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2708,10 +2717,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122152081</v>
+        <v>122152052</v>
       </c>
       <c r="B21" t="n">
-        <v>79733</v>
+        <v>79732</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2724,34 +2733,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Bergsvik, Jmt</t>
+          <t>Brynje, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>479613</v>
+        <v>479717</v>
       </c>
       <c r="R21" t="n">
-        <v>6951267</v>
+        <v>6951549</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2912,10 +2921,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122152057</v>
+        <v>122152028</v>
       </c>
       <c r="B23" t="n">
-        <v>74757</v>
+        <v>78651</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2928,34 +2937,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1467</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Brynje, Jmt</t>
+          <t>Bergsvik, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>479727</v>
+        <v>479733</v>
       </c>
       <c r="R23" t="n">
-        <v>6951580</v>
+        <v>6951321</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -2988,11 +2997,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2024-08-30</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>På granstubbe intill bäck.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3019,7 +3023,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122152034</v>
+        <v>122152049</v>
       </c>
       <c r="B24" t="n">
         <v>79732</v>
@@ -3059,10 +3063,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>479844</v>
+        <v>479749</v>
       </c>
       <c r="R24" t="n">
-        <v>6951363</v>
+        <v>6951522</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3121,10 +3125,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122152039</v>
+        <v>122154343</v>
       </c>
       <c r="B25" t="n">
-        <v>79733</v>
+        <v>94228</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3133,25 +3137,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2081</v>
+        <v>2387</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Källpraktmossa</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Pseudobryum cinclidioides</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Huebener) T.J.Kop.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3161,10 +3165,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>479768</v>
+        <v>479547</v>
       </c>
       <c r="R25" t="n">
-        <v>6951511</v>
+        <v>6951577</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3191,12 +3195,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-10-05</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-10-05</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3211,12 +3215,12 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
@@ -3334,10 +3338,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122154346</v>
+        <v>122152050</v>
       </c>
       <c r="B27" t="n">
-        <v>57532</v>
+        <v>79733</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3350,21 +3354,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>103021</v>
+        <v>2081</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3374,10 +3378,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>479569</v>
+        <v>479716</v>
       </c>
       <c r="R27" t="n">
-        <v>6951576</v>
+        <v>6951549</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3404,12 +3408,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2024-10-05</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2024-10-05</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3424,22 +3428,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122154345</v>
+        <v>122152064</v>
       </c>
       <c r="B28" t="n">
-        <v>97151</v>
+        <v>98538</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3452,21 +3456,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>221945</v>
+        <v>219880</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3476,10 +3480,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>479596</v>
+        <v>479647</v>
       </c>
       <c r="R28" t="n">
-        <v>6951595</v>
+        <v>6951498</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3506,12 +3510,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2024-10-05</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2024-10-05</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3526,22 +3530,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122152079</v>
+        <v>122152068</v>
       </c>
       <c r="B29" t="n">
-        <v>79733</v>
+        <v>95749</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3554,34 +3558,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2081</v>
+        <v>53</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Bergsvik, Jmt</t>
+          <t>Brynje, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>479619</v>
+        <v>479630</v>
       </c>
       <c r="R29" t="n">
-        <v>6951287</v>
+        <v>6951446</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3614,6 +3618,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2024-08-30</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>På murken granlåga i gransumpskog.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3640,10 +3649,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122152031</v>
+        <v>122152034</v>
       </c>
       <c r="B30" t="n">
-        <v>79733</v>
+        <v>79732</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3656,21 +3665,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3680,10 +3689,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>479817</v>
+        <v>479844</v>
       </c>
       <c r="R30" t="n">
-        <v>6951441</v>
+        <v>6951363</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3742,10 +3751,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122152045</v>
+        <v>122152047</v>
       </c>
       <c r="B31" t="n">
-        <v>79732</v>
+        <v>79761</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3754,25 +3763,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3782,10 +3791,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>479758</v>
+        <v>479750</v>
       </c>
       <c r="R31" t="n">
-        <v>6951496</v>
+        <v>6951517</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3844,10 +3853,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122154343</v>
+        <v>122152076</v>
       </c>
       <c r="B32" t="n">
-        <v>94223</v>
+        <v>79732</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3856,38 +3865,38 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>2387</v>
+        <v>6458</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Källpraktmossa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Pseudobryum cinclidioides</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Huebener) T.J.Kop.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Brynje, Jmt</t>
+          <t>Bergsvik, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>479547</v>
+        <v>479653</v>
       </c>
       <c r="R32" t="n">
-        <v>6951577</v>
+        <v>6951307</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -3914,12 +3923,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2024-10-05</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2024-10-05</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3934,22 +3943,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122152074</v>
+        <v>122154346</v>
       </c>
       <c r="B33" t="n">
-        <v>79733</v>
+        <v>57532</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3962,34 +3971,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>2081</v>
+        <v>103021</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Bergsvik, Jmt</t>
+          <t>Brynje, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>479654</v>
+        <v>479569</v>
       </c>
       <c r="R33" t="n">
-        <v>6951309</v>
+        <v>6951576</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4016,12 +4025,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-10-05</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-10-05</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4036,22 +4045,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122152028</v>
+        <v>122152079</v>
       </c>
       <c r="B34" t="n">
-        <v>78651</v>
+        <v>79733</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4064,21 +4073,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4088,10 +4097,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>479733</v>
+        <v>479619</v>
       </c>
       <c r="R34" t="n">
-        <v>6951321</v>
+        <v>6951287</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4150,10 +4159,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122152068</v>
+        <v>122152041</v>
       </c>
       <c r="B35" t="n">
-        <v>95744</v>
+        <v>79732</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4166,21 +4175,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>53</v>
+        <v>6458</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4190,10 +4199,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>479630</v>
+        <v>479769</v>
       </c>
       <c r="R35" t="n">
-        <v>6951446</v>
+        <v>6951516</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4226,11 +4235,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2024-08-30</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>På murken granlåga i gransumpskog.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4257,10 +4261,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122152044</v>
+        <v>122152029</v>
       </c>
       <c r="B36" t="n">
-        <v>79733</v>
+        <v>79761</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4269,25 +4273,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>2081</v>
+        <v>6462</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4297,10 +4301,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>479757</v>
+        <v>479816</v>
       </c>
       <c r="R36" t="n">
-        <v>6951495</v>
+        <v>6951443</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4359,10 +4363,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122152047</v>
+        <v>122154338</v>
       </c>
       <c r="B37" t="n">
-        <v>79761</v>
+        <v>79732</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4371,25 +4375,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4399,10 +4403,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>479750</v>
+        <v>479524</v>
       </c>
       <c r="R37" t="n">
-        <v>6951517</v>
+        <v>6951553</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4429,12 +4433,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-10-05</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-10-05</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4449,22 +4453,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122152064</v>
+        <v>122152033</v>
       </c>
       <c r="B38" t="n">
-        <v>98533</v>
+        <v>79732</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4473,25 +4477,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>219880</v>
+        <v>6458</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4501,10 +4505,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>479647</v>
+        <v>479817</v>
       </c>
       <c r="R38" t="n">
-        <v>6951498</v>
+        <v>6951441</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4563,7 +4567,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122152073</v>
+        <v>122152031</v>
       </c>
       <c r="B39" t="n">
         <v>79733</v>
@@ -4599,14 +4603,14 @@
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Bergsvik, Jmt</t>
+          <t>Brynje, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>479656</v>
+        <v>479817</v>
       </c>
       <c r="R39" t="n">
-        <v>6951332</v>
+        <v>6951441</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4665,10 +4669,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122152023</v>
+        <v>122152039</v>
       </c>
       <c r="B40" t="n">
-        <v>56581</v>
+        <v>79733</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4681,38 +4685,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>102612</v>
+        <v>2081</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Bergsvik, Jmt</t>
+          <t>Brynje, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>479776</v>
+        <v>479768</v>
       </c>
       <c r="R40" t="n">
-        <v>6951285</v>
+        <v>6951511</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4771,10 +4771,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122152029</v>
+        <v>122152073</v>
       </c>
       <c r="B41" t="n">
-        <v>79761</v>
+        <v>79733</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4783,38 +4783,38 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6462</v>
+        <v>2081</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Brynje, Jmt</t>
+          <t>Bergsvik, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>479816</v>
+        <v>479656</v>
       </c>
       <c r="R41" t="n">
-        <v>6951443</v>
+        <v>6951332</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -4873,7 +4873,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122152054</v>
+        <v>122152045</v>
       </c>
       <c r="B42" t="n">
         <v>79732</v>
@@ -4913,10 +4913,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>479731</v>
+        <v>479758</v>
       </c>
       <c r="R42" t="n">
-        <v>6951554</v>
+        <v>6951496</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>

--- a/artfynd/A 18303-2024 artfynd.xlsx
+++ b/artfynd/A 18303-2024 artfynd.xlsx
@@ -4567,7 +4567,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122152031</v>
+        <v>122152039</v>
       </c>
       <c r="B39" t="n">
         <v>79733</v>
@@ -4607,10 +4607,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>479817</v>
+        <v>479768</v>
       </c>
       <c r="R39" t="n">
-        <v>6951441</v>
+        <v>6951511</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4669,7 +4669,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122152039</v>
+        <v>122152073</v>
       </c>
       <c r="B40" t="n">
         <v>79733</v>
@@ -4705,14 +4705,14 @@
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Brynje, Jmt</t>
+          <t>Bergsvik, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>479768</v>
+        <v>479656</v>
       </c>
       <c r="R40" t="n">
-        <v>6951511</v>
+        <v>6951332</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4771,7 +4771,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122152073</v>
+        <v>122152031</v>
       </c>
       <c r="B41" t="n">
         <v>79733</v>
@@ -4807,14 +4807,14 @@
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Bergsvik, Jmt</t>
+          <t>Brynje, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>479656</v>
+        <v>479817</v>
       </c>
       <c r="R41" t="n">
-        <v>6951332</v>
+        <v>6951441</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>

--- a/artfynd/A 18303-2024 artfynd.xlsx
+++ b/artfynd/A 18303-2024 artfynd.xlsx
@@ -1280,10 +1280,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122152142</v>
+        <v>122152068</v>
       </c>
       <c r="B7" t="n">
-        <v>78651</v>
+        <v>95758</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1296,34 +1296,29 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
+        <v>53</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Bergsvik, Jmt</t>
+          <t>Brynje, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>479790</v>
+        <v>479630</v>
       </c>
       <c r="R7" t="n">
-        <v>6951160</v>
+        <v>6951446</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1350,12 +1345,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2024-08-30</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>På murken granlåga i gransumpskog.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1382,10 +1382,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122152071</v>
+        <v>122152052</v>
       </c>
       <c r="B8" t="n">
-        <v>79732</v>
+        <v>79733</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1400,11 +1400,6 @@
       <c r="E8" t="n">
         <v>6458</v>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Lunglav</t>
-        </is>
-      </c>
       <c r="G8" t="inlineStr">
         <is>
           <t>Lobaria pulmonaria</t>
@@ -1418,14 +1413,14 @@
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Bergsvik, Jmt</t>
+          <t>Brynje, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>479656</v>
+        <v>479717</v>
       </c>
       <c r="R8" t="n">
-        <v>6951332</v>
+        <v>6951549</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1484,7 +1479,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122152074</v>
+        <v>122152054</v>
       </c>
       <c r="B9" t="n">
         <v>79733</v>
@@ -1500,34 +1495,29 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2081</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Skrovellav</t>
-        </is>
+        <v>6458</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Bergsvik, Jmt</t>
+          <t>Brynje, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>479654</v>
+        <v>479731</v>
       </c>
       <c r="R9" t="n">
-        <v>6951309</v>
+        <v>6951554</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1586,10 +1576,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122152077</v>
+        <v>122152047</v>
       </c>
       <c r="B10" t="n">
-        <v>79732</v>
+        <v>79762</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1598,38 +1588,33 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Lunglav</t>
-        </is>
+        <v>6462</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Bergsvik, Jmt</t>
+          <t>Brynje, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>479619</v>
+        <v>479750</v>
       </c>
       <c r="R10" t="n">
-        <v>6951287</v>
+        <v>6951517</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1688,10 +1673,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122154345</v>
+        <v>122152041</v>
       </c>
       <c r="B11" t="n">
-        <v>97156</v>
+        <v>79733</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1700,25 +1685,20 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221945</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Revlummer</t>
-        </is>
+        <v>6458</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1728,10 +1708,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>479596</v>
+        <v>479769</v>
       </c>
       <c r="R11" t="n">
-        <v>6951595</v>
+        <v>6951516</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1758,12 +1738,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-10-05</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-10-05</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1778,22 +1758,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122152055</v>
+        <v>122152077</v>
       </c>
       <c r="B12" t="n">
-        <v>90808</v>
+        <v>79733</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1806,34 +1786,29 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Ullticka</t>
-        </is>
+        <v>6458</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Brynje, Jmt</t>
+          <t>Bergsvik, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>479734</v>
+        <v>479619</v>
       </c>
       <c r="R12" t="n">
-        <v>6951563</v>
+        <v>6951287</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1892,10 +1867,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122152037</v>
+        <v>122154346</v>
       </c>
       <c r="B13" t="n">
-        <v>79761</v>
+        <v>57532</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1904,25 +1879,20 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6462</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Stuplav</t>
-        </is>
+        <v>103021</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1932,10 +1902,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>479767</v>
+        <v>479569</v>
       </c>
       <c r="R13" t="n">
-        <v>6951509</v>
+        <v>6951576</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1962,12 +1932,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-10-05</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-10-05</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1982,22 +1952,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122152024</v>
+        <v>122154343</v>
       </c>
       <c r="B14" t="n">
-        <v>79733</v>
+        <v>94237</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2006,38 +1976,33 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2081</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Skrovellav</t>
-        </is>
+        <v>2387</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Pseudobryum cinclidioides</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Huebener) T.J.Kop.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Bergsvik, Jmt</t>
+          <t>Brynje, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>479764</v>
+        <v>479547</v>
       </c>
       <c r="R14" t="n">
-        <v>6951289</v>
+        <v>6951577</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2064,12 +2029,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-10-05</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-10-05</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2084,22 +2049,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122152054</v>
+        <v>122152142</v>
       </c>
       <c r="B15" t="n">
-        <v>79732</v>
+        <v>78652</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2112,34 +2077,29 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Lunglav</t>
-        </is>
+        <v>6425</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Brynje, Jmt</t>
+          <t>Bergsvik, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>479731</v>
+        <v>479790</v>
       </c>
       <c r="R15" t="n">
-        <v>6951554</v>
+        <v>6951160</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2166,12 +2126,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2198,10 +2158,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122152057</v>
+        <v>122152081</v>
       </c>
       <c r="B16" t="n">
-        <v>74757</v>
+        <v>79734</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2214,34 +2174,29 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1467</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Rödbrun blekspik</t>
-        </is>
+        <v>2081</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Brynje, Jmt</t>
+          <t>Bergsvik, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>479727</v>
+        <v>479613</v>
       </c>
       <c r="R16" t="n">
-        <v>6951580</v>
+        <v>6951267</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2274,11 +2229,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2024-08-30</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>På granstubbe intill bäck.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2305,10 +2255,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122152026</v>
+        <v>122152034</v>
       </c>
       <c r="B17" t="n">
-        <v>79732</v>
+        <v>79733</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2323,11 +2273,6 @@
       <c r="E17" t="n">
         <v>6458</v>
       </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Lunglav</t>
-        </is>
-      </c>
       <c r="G17" t="inlineStr">
         <is>
           <t>Lobaria pulmonaria</t>
@@ -2341,14 +2286,14 @@
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Bergsvik, Jmt</t>
+          <t>Brynje, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>479764</v>
+        <v>479844</v>
       </c>
       <c r="R17" t="n">
-        <v>6951290</v>
+        <v>6951363</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2407,10 +2352,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122152081</v>
+        <v>122152050</v>
       </c>
       <c r="B18" t="n">
-        <v>79733</v>
+        <v>79734</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2425,11 +2370,6 @@
       <c r="E18" t="n">
         <v>2081</v>
       </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>Skrovellav</t>
-        </is>
-      </c>
       <c r="G18" t="inlineStr">
         <is>
           <t>Lobaria scrobiculata</t>
@@ -2443,14 +2383,14 @@
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Bergsvik, Jmt</t>
+          <t>Brynje, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>479613</v>
+        <v>479716</v>
       </c>
       <c r="R18" t="n">
-        <v>6951267</v>
+        <v>6951549</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2509,10 +2449,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122152023</v>
+        <v>122152037</v>
       </c>
       <c r="B19" t="n">
-        <v>56581</v>
+        <v>79762</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2521,42 +2461,33 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>102612</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>Järpe</t>
-        </is>
+        <v>6462</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Bergsvik, Jmt</t>
+          <t>Brynje, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>479776</v>
+        <v>479767</v>
       </c>
       <c r="R19" t="n">
-        <v>6951285</v>
+        <v>6951509</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2615,7 +2546,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122152044</v>
+        <v>122152045</v>
       </c>
       <c r="B20" t="n">
         <v>79733</v>
@@ -2631,21 +2562,16 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2081</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>Skrovellav</t>
-        </is>
+        <v>6458</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2655,10 +2581,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>479757</v>
+        <v>479758</v>
       </c>
       <c r="R20" t="n">
-        <v>6951495</v>
+        <v>6951496</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2717,10 +2643,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122152052</v>
+        <v>122154345</v>
       </c>
       <c r="B21" t="n">
-        <v>79732</v>
+        <v>97165</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2729,25 +2655,20 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Lunglav</t>
-        </is>
+        <v>221945</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2757,10 +2678,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>479717</v>
+        <v>479596</v>
       </c>
       <c r="R21" t="n">
-        <v>6951549</v>
+        <v>6951595</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2787,12 +2708,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-10-05</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-10-05</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2807,22 +2728,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122152042</v>
+        <v>122152039</v>
       </c>
       <c r="B22" t="n">
-        <v>79761</v>
+        <v>79734</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2831,25 +2752,20 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6462</v>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>Stuplav</t>
-        </is>
+        <v>2081</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2859,10 +2775,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>479757</v>
+        <v>479768</v>
       </c>
       <c r="R22" t="n">
-        <v>6951495</v>
+        <v>6951511</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2921,10 +2837,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122152028</v>
+        <v>122152076</v>
       </c>
       <c r="B23" t="n">
-        <v>78651</v>
+        <v>79733</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2937,21 +2853,16 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
+        <v>6458</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2961,10 +2872,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>479733</v>
+        <v>479653</v>
       </c>
       <c r="R23" t="n">
-        <v>6951321</v>
+        <v>6951307</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3023,10 +2934,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122152049</v>
+        <v>122152033</v>
       </c>
       <c r="B24" t="n">
-        <v>79732</v>
+        <v>79733</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3041,11 +2952,6 @@
       <c r="E24" t="n">
         <v>6458</v>
       </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>Lunglav</t>
-        </is>
-      </c>
       <c r="G24" t="inlineStr">
         <is>
           <t>Lobaria pulmonaria</t>
@@ -3063,10 +2969,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>479749</v>
+        <v>479817</v>
       </c>
       <c r="R24" t="n">
-        <v>6951522</v>
+        <v>6951441</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3125,10 +3031,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122154343</v>
+        <v>122152031</v>
       </c>
       <c r="B25" t="n">
-        <v>94228</v>
+        <v>79734</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3137,25 +3043,20 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2387</v>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>Källpraktmossa</t>
-        </is>
+        <v>2081</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Pseudobryum cinclidioides</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Huebener) T.J.Kop.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3165,10 +3066,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>479547</v>
+        <v>479817</v>
       </c>
       <c r="R25" t="n">
-        <v>6951577</v>
+        <v>6951441</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3195,12 +3096,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2024-10-05</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2024-10-05</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3215,22 +3116,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122152021</v>
+        <v>122152024</v>
       </c>
       <c r="B26" t="n">
-        <v>56589</v>
+        <v>79734</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3239,42 +3140,33 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100138</v>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>Tjäder</t>
-        </is>
+        <v>2081</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Bergsvik, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>479770</v>
+        <v>479764</v>
       </c>
       <c r="R26" t="n">
-        <v>6951296</v>
+        <v>6951289</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3307,11 +3199,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2024-08-30</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Uppflog.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3338,7 +3225,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122152050</v>
+        <v>122152049</v>
       </c>
       <c r="B27" t="n">
         <v>79733</v>
@@ -3354,21 +3241,16 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2081</v>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>Skrovellav</t>
-        </is>
+        <v>6458</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3378,10 +3260,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>479716</v>
+        <v>479749</v>
       </c>
       <c r="R27" t="n">
-        <v>6951549</v>
+        <v>6951522</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3440,10 +3322,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122152064</v>
+        <v>122152042</v>
       </c>
       <c r="B28" t="n">
-        <v>98538</v>
+        <v>79762</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3456,21 +3338,16 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>219880</v>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>Kransrams</t>
-        </is>
+        <v>6462</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3480,10 +3357,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>479647</v>
+        <v>479757</v>
       </c>
       <c r="R28" t="n">
-        <v>6951498</v>
+        <v>6951495</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3542,10 +3419,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122152068</v>
+        <v>122152026</v>
       </c>
       <c r="B29" t="n">
-        <v>95749</v>
+        <v>79733</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3558,34 +3435,29 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>53</v>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>Vedtrappmossa</t>
-        </is>
+        <v>6458</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Brynje, Jmt</t>
+          <t>Bergsvik, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>479630</v>
+        <v>479764</v>
       </c>
       <c r="R29" t="n">
-        <v>6951446</v>
+        <v>6951290</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3618,11 +3490,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2024-08-30</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>På murken granlåga i gransumpskog.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3649,10 +3516,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122152034</v>
+        <v>122152029</v>
       </c>
       <c r="B30" t="n">
-        <v>79732</v>
+        <v>79762</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3661,25 +3528,20 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6458</v>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>Lunglav</t>
-        </is>
+        <v>6462</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3689,10 +3551,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>479844</v>
+        <v>479816</v>
       </c>
       <c r="R30" t="n">
-        <v>6951363</v>
+        <v>6951443</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3751,10 +3613,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122152047</v>
+        <v>122152028</v>
       </c>
       <c r="B31" t="n">
-        <v>79761</v>
+        <v>78652</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3763,38 +3625,33 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6462</v>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>Stuplav</t>
-        </is>
+        <v>6425</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Brynje, Jmt</t>
+          <t>Bergsvik, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>479750</v>
+        <v>479733</v>
       </c>
       <c r="R31" t="n">
-        <v>6951517</v>
+        <v>6951321</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3853,10 +3710,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122152076</v>
+        <v>122152023</v>
       </c>
       <c r="B32" t="n">
-        <v>79732</v>
+        <v>56581</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3869,34 +3726,33 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6458</v>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>Lunglav</t>
-        </is>
+        <v>102612</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Bergsvik, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>479653</v>
+        <v>479776</v>
       </c>
       <c r="R32" t="n">
-        <v>6951307</v>
+        <v>6951285</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -3955,10 +3811,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122154346</v>
+        <v>122152057</v>
       </c>
       <c r="B33" t="n">
-        <v>57532</v>
+        <v>74758</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3971,21 +3827,16 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>103021</v>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>Talltita</t>
-        </is>
+        <v>1467</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3995,10 +3846,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>479569</v>
+        <v>479727</v>
       </c>
       <c r="R33" t="n">
-        <v>6951576</v>
+        <v>6951580</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4025,12 +3876,17 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2024-10-05</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2024-10-05</t>
+          <t>2024-08-30</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>På granstubbe intill bäck.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4045,22 +3901,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122152079</v>
+        <v>122152064</v>
       </c>
       <c r="B34" t="n">
-        <v>79733</v>
+        <v>98547</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4069,38 +3925,33 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>2081</v>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>Skrovellav</t>
-        </is>
+        <v>219880</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Bergsvik, Jmt</t>
+          <t>Brynje, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>479619</v>
+        <v>479647</v>
       </c>
       <c r="R34" t="n">
-        <v>6951287</v>
+        <v>6951498</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4159,10 +4010,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122152041</v>
+        <v>122152079</v>
       </c>
       <c r="B35" t="n">
-        <v>79732</v>
+        <v>79734</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4175,34 +4026,29 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6458</v>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>Lunglav</t>
-        </is>
+        <v>2081</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Brynje, Jmt</t>
+          <t>Bergsvik, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>479769</v>
+        <v>479619</v>
       </c>
       <c r="R35" t="n">
-        <v>6951516</v>
+        <v>6951287</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4261,10 +4107,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122152029</v>
+        <v>122152074</v>
       </c>
       <c r="B36" t="n">
-        <v>79761</v>
+        <v>79734</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4273,38 +4119,33 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6462</v>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>Stuplav</t>
-        </is>
+        <v>2081</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Brynje, Jmt</t>
+          <t>Bergsvik, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>479816</v>
+        <v>479654</v>
       </c>
       <c r="R36" t="n">
-        <v>6951443</v>
+        <v>6951309</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4366,7 +4207,7 @@
         <v>122154338</v>
       </c>
       <c r="B37" t="n">
-        <v>79732</v>
+        <v>79733</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4380,11 +4221,6 @@
       </c>
       <c r="E37" t="n">
         <v>6458</v>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>Lunglav</t>
-        </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -4465,10 +4301,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122152033</v>
+        <v>122152055</v>
       </c>
       <c r="B38" t="n">
-        <v>79732</v>
+        <v>90813</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4481,21 +4317,16 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6458</v>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>Lunglav</t>
-        </is>
+        <v>1202</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4505,10 +4336,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>479817</v>
+        <v>479734</v>
       </c>
       <c r="R38" t="n">
-        <v>6951441</v>
+        <v>6951563</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4567,10 +4398,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122152039</v>
+        <v>122152073</v>
       </c>
       <c r="B39" t="n">
-        <v>79733</v>
+        <v>79734</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4585,11 +4416,6 @@
       <c r="E39" t="n">
         <v>2081</v>
       </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>Skrovellav</t>
-        </is>
-      </c>
       <c r="G39" t="inlineStr">
         <is>
           <t>Lobaria scrobiculata</t>
@@ -4603,14 +4429,14 @@
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Brynje, Jmt</t>
+          <t>Bergsvik, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>479768</v>
+        <v>479656</v>
       </c>
       <c r="R39" t="n">
-        <v>6951511</v>
+        <v>6951332</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4669,7 +4495,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122152073</v>
+        <v>122152071</v>
       </c>
       <c r="B40" t="n">
         <v>79733</v>
@@ -4685,21 +4511,16 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>2081</v>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>Skrovellav</t>
-        </is>
+        <v>6458</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4771,10 +4592,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122152031</v>
+        <v>122152044</v>
       </c>
       <c r="B41" t="n">
-        <v>79733</v>
+        <v>79734</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4789,11 +4610,6 @@
       <c r="E41" t="n">
         <v>2081</v>
       </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>Skrovellav</t>
-        </is>
-      </c>
       <c r="G41" t="inlineStr">
         <is>
           <t>Lobaria scrobiculata</t>
@@ -4811,10 +4627,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>479817</v>
+        <v>479757</v>
       </c>
       <c r="R41" t="n">
-        <v>6951441</v>
+        <v>6951495</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -4873,10 +4689,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122152045</v>
+        <v>122152021</v>
       </c>
       <c r="B42" t="n">
-        <v>79732</v>
+        <v>56589</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4885,38 +4701,37 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6458</v>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>Lunglav</t>
-        </is>
+        <v>100138</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Brynje, Jmt</t>
+          <t>Bergsvik, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>479758</v>
+        <v>479770</v>
       </c>
       <c r="R42" t="n">
-        <v>6951496</v>
+        <v>6951296</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -4949,6 +4764,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2024-08-30</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Uppflog.</t>
         </is>
       </c>
       <c r="AD42" t="b">

--- a/artfynd/A 18303-2024 artfynd.xlsx
+++ b/artfynd/A 18303-2024 artfynd.xlsx
@@ -1770,10 +1770,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122152077</v>
+        <v>122152142</v>
       </c>
       <c r="B12" t="n">
-        <v>79733</v>
+        <v>78652</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1786,16 +1786,16 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1805,10 +1805,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>479619</v>
+        <v>479790</v>
       </c>
       <c r="R12" t="n">
-        <v>6951287</v>
+        <v>6951160</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1835,12 +1835,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1867,10 +1867,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122154346</v>
+        <v>122154343</v>
       </c>
       <c r="B13" t="n">
-        <v>57532</v>
+        <v>94237</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1879,20 +1879,20 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103021</v>
+        <v>2387</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Pseudobryum cinclidioides</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Huebener) T.J.Kop.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1902,10 +1902,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>479569</v>
+        <v>479547</v>
       </c>
       <c r="R13" t="n">
-        <v>6951576</v>
+        <v>6951577</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1964,10 +1964,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122154343</v>
+        <v>122152077</v>
       </c>
       <c r="B14" t="n">
-        <v>94237</v>
+        <v>79733</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1976,33 +1976,33 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2387</v>
+        <v>6458</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pseudobryum cinclidioides</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Huebener) T.J.Kop.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Brynje, Jmt</t>
+          <t>Bergsvik, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>479547</v>
+        <v>479619</v>
       </c>
       <c r="R14" t="n">
-        <v>6951577</v>
+        <v>6951287</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2029,12 +2029,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-10-05</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-10-05</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2049,22 +2049,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122152142</v>
+        <v>122154346</v>
       </c>
       <c r="B15" t="n">
-        <v>78652</v>
+        <v>57532</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2077,29 +2077,29 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Bergsvik, Jmt</t>
+          <t>Brynje, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>479790</v>
+        <v>479569</v>
       </c>
       <c r="R15" t="n">
-        <v>6951160</v>
+        <v>6951576</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2126,12 +2126,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2024-10-05</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2024-10-05</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2146,12 +2146,12 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
@@ -3031,10 +3031,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122152031</v>
+        <v>122152049</v>
       </c>
       <c r="B25" t="n">
-        <v>79734</v>
+        <v>79733</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3047,16 +3047,16 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3066,10 +3066,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>479817</v>
+        <v>479749</v>
       </c>
       <c r="R25" t="n">
-        <v>6951441</v>
+        <v>6951522</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3128,7 +3128,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122152024</v>
+        <v>122152031</v>
       </c>
       <c r="B26" t="n">
         <v>79734</v>
@@ -3159,14 +3159,14 @@
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Bergsvik, Jmt</t>
+          <t>Brynje, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>479764</v>
+        <v>479817</v>
       </c>
       <c r="R26" t="n">
-        <v>6951289</v>
+        <v>6951441</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3225,10 +3225,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122152049</v>
+        <v>122152024</v>
       </c>
       <c r="B27" t="n">
-        <v>79733</v>
+        <v>79734</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3241,29 +3241,29 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Brynje, Jmt</t>
+          <t>Bergsvik, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>479749</v>
+        <v>479764</v>
       </c>
       <c r="R27" t="n">
-        <v>6951522</v>
+        <v>6951289</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>

--- a/artfynd/A 18303-2024 artfynd.xlsx
+++ b/artfynd/A 18303-2024 artfynd.xlsx
@@ -1280,10 +1280,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122152068</v>
+        <v>122152052</v>
       </c>
       <c r="B7" t="n">
-        <v>95758</v>
+        <v>79733</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1296,16 +1296,16 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>53</v>
+        <v>6458</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1315,10 +1315,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>479630</v>
+        <v>479717</v>
       </c>
       <c r="R7" t="n">
-        <v>6951446</v>
+        <v>6951549</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1351,11 +1351,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-08-30</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>På murken granlåga i gransumpskog.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1382,10 +1377,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122152052</v>
+        <v>122152068</v>
       </c>
       <c r="B8" t="n">
-        <v>79733</v>
+        <v>95758</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1398,16 +1393,16 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>53</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1417,10 +1412,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>479717</v>
+        <v>479630</v>
       </c>
       <c r="R8" t="n">
-        <v>6951549</v>
+        <v>6951446</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1453,6 +1448,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-08-30</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>På murken granlåga i gransumpskog.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -3710,10 +3710,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122152023</v>
+        <v>122152057</v>
       </c>
       <c r="B32" t="n">
-        <v>56581</v>
+        <v>74758</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3726,33 +3726,29 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>102612</v>
+        <v>1467</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Bergsvik, Jmt</t>
+          <t>Brynje, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>479776</v>
+        <v>479727</v>
       </c>
       <c r="R32" t="n">
-        <v>6951285</v>
+        <v>6951580</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -3785,6 +3781,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2024-08-30</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>På granstubbe intill bäck.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3811,10 +3812,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122152057</v>
+        <v>122152023</v>
       </c>
       <c r="B33" t="n">
-        <v>74758</v>
+        <v>56581</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3827,29 +3828,33 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1467</v>
+        <v>102612</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Brynje, Jmt</t>
+          <t>Bergsvik, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>479727</v>
+        <v>479776</v>
       </c>
       <c r="R33" t="n">
-        <v>6951580</v>
+        <v>6951285</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -3882,11 +3887,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2024-08-30</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>På granstubbe intill bäck.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4204,10 +4204,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122154338</v>
+        <v>122152073</v>
       </c>
       <c r="B37" t="n">
-        <v>79733</v>
+        <v>79734</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4220,29 +4220,29 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Brynje, Jmt</t>
+          <t>Bergsvik, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>479524</v>
+        <v>479656</v>
       </c>
       <c r="R37" t="n">
-        <v>6951553</v>
+        <v>6951332</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4269,12 +4269,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2024-10-05</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2024-10-05</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4289,12 +4289,12 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
@@ -4398,10 +4398,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122152073</v>
+        <v>122154338</v>
       </c>
       <c r="B39" t="n">
-        <v>79734</v>
+        <v>79733</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4414,29 +4414,29 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Bergsvik, Jmt</t>
+          <t>Brynje, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>479656</v>
+        <v>479524</v>
       </c>
       <c r="R39" t="n">
-        <v>6951332</v>
+        <v>6951553</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4463,12 +4463,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-10-05</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-10-05</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4483,12 +4483,12 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>

--- a/artfynd/A 18303-2024 artfynd.xlsx
+++ b/artfynd/A 18303-2024 artfynd.xlsx
@@ -1280,10 +1280,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122152052</v>
+        <v>122152068</v>
       </c>
       <c r="B7" t="n">
-        <v>79733</v>
+        <v>95771</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1296,16 +1296,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>53</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1315,10 +1320,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>479717</v>
+        <v>479630</v>
       </c>
       <c r="R7" t="n">
-        <v>6951549</v>
+        <v>6951446</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1351,6 +1356,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-08-30</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>På murken granlåga i gransumpskog.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1377,10 +1387,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122152068</v>
+        <v>122152024</v>
       </c>
       <c r="B8" t="n">
-        <v>95758</v>
+        <v>79738</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1393,29 +1403,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>53</v>
+        <v>2081</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Skrovellav</t>
+        </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Brynje, Jmt</t>
+          <t>Bergsvik, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>479630</v>
+        <v>479764</v>
       </c>
       <c r="R8" t="n">
-        <v>6951446</v>
+        <v>6951289</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1448,11 +1463,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-08-30</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>På murken granlåga i gransumpskog.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1479,10 +1489,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122152054</v>
+        <v>122152055</v>
       </c>
       <c r="B9" t="n">
-        <v>79733</v>
+        <v>90826</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1495,16 +1505,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>1202</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1514,10 +1529,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>479731</v>
+        <v>479734</v>
       </c>
       <c r="R9" t="n">
-        <v>6951554</v>
+        <v>6951563</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1576,10 +1591,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122152047</v>
+        <v>122152039</v>
       </c>
       <c r="B10" t="n">
-        <v>79762</v>
+        <v>79738</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1588,20 +1603,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6462</v>
+        <v>2081</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Skrovellav</t>
+        </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1611,10 +1631,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>479750</v>
+        <v>479768</v>
       </c>
       <c r="R10" t="n">
-        <v>6951517</v>
+        <v>6951511</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1673,10 +1693,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122152041</v>
+        <v>122152037</v>
       </c>
       <c r="B11" t="n">
-        <v>79733</v>
+        <v>79766</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1685,20 +1705,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>6462</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1708,10 +1733,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>479769</v>
+        <v>479767</v>
       </c>
       <c r="R11" t="n">
-        <v>6951516</v>
+        <v>6951509</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1770,10 +1795,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122152142</v>
+        <v>122152031</v>
       </c>
       <c r="B12" t="n">
-        <v>78652</v>
+        <v>79738</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1786,29 +1811,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>2081</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Skrovellav</t>
+        </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Bergsvik, Jmt</t>
+          <t>Brynje, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>479790</v>
+        <v>479817</v>
       </c>
       <c r="R12" t="n">
-        <v>6951160</v>
+        <v>6951441</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1835,12 +1865,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1867,10 +1897,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122154343</v>
+        <v>122152045</v>
       </c>
       <c r="B13" t="n">
-        <v>94237</v>
+        <v>79737</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1879,20 +1909,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2387</v>
+        <v>6458</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pseudobryum cinclidioides</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Huebener) T.J.Kop.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1902,10 +1937,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>479547</v>
+        <v>479758</v>
       </c>
       <c r="R13" t="n">
-        <v>6951577</v>
+        <v>6951496</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1932,12 +1967,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2024-10-05</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2024-10-05</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1952,22 +1987,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122152077</v>
+        <v>122152028</v>
       </c>
       <c r="B14" t="n">
-        <v>79733</v>
+        <v>78656</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1980,16 +2015,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>6425</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1999,10 +2039,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>479619</v>
+        <v>479733</v>
       </c>
       <c r="R14" t="n">
-        <v>6951287</v>
+        <v>6951321</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2061,10 +2101,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122154346</v>
+        <v>122152142</v>
       </c>
       <c r="B15" t="n">
-        <v>57532</v>
+        <v>78656</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2077,29 +2117,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103021</v>
+        <v>6425</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Brynje, Jmt</t>
+          <t>Bergsvik, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>479569</v>
+        <v>479790</v>
       </c>
       <c r="R15" t="n">
-        <v>6951576</v>
+        <v>6951160</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2126,12 +2171,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2024-10-05</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2024-10-05</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2146,22 +2191,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122152081</v>
+        <v>122152052</v>
       </c>
       <c r="B16" t="n">
-        <v>79734</v>
+        <v>79737</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2174,29 +2219,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2081</v>
+        <v>6458</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Bergsvik, Jmt</t>
+          <t>Brynje, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>479613</v>
+        <v>479717</v>
       </c>
       <c r="R16" t="n">
-        <v>6951267</v>
+        <v>6951549</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2255,10 +2305,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122152034</v>
+        <v>122152079</v>
       </c>
       <c r="B17" t="n">
-        <v>79733</v>
+        <v>79738</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2271,29 +2321,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>2081</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Skrovellav</t>
+        </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Brynje, Jmt</t>
+          <t>Bergsvik, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>479844</v>
+        <v>479619</v>
       </c>
       <c r="R17" t="n">
-        <v>6951363</v>
+        <v>6951287</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2352,10 +2407,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122152050</v>
+        <v>122152044</v>
       </c>
       <c r="B18" t="n">
-        <v>79734</v>
+        <v>79738</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2370,6 +2425,11 @@
       <c r="E18" t="n">
         <v>2081</v>
       </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Skrovellav</t>
+        </is>
+      </c>
       <c r="G18" t="inlineStr">
         <is>
           <t>Lobaria scrobiculata</t>
@@ -2387,10 +2447,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>479716</v>
+        <v>479757</v>
       </c>
       <c r="R18" t="n">
-        <v>6951549</v>
+        <v>6951495</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2449,10 +2509,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122152037</v>
+        <v>122152026</v>
       </c>
       <c r="B19" t="n">
-        <v>79762</v>
+        <v>79737</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2461,33 +2521,38 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6462</v>
+        <v>6458</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Brynje, Jmt</t>
+          <t>Bergsvik, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>479767</v>
+        <v>479764</v>
       </c>
       <c r="R19" t="n">
-        <v>6951509</v>
+        <v>6951290</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2546,10 +2611,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122152045</v>
+        <v>122154343</v>
       </c>
       <c r="B20" t="n">
-        <v>79733</v>
+        <v>94250</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2558,20 +2623,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>2387</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Källpraktmossa</t>
+        </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pseudobryum cinclidioides</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Huebener) T.J.Kop.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2581,10 +2651,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>479758</v>
+        <v>479547</v>
       </c>
       <c r="R20" t="n">
-        <v>6951496</v>
+        <v>6951577</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2611,12 +2681,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-10-05</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-10-05</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2631,22 +2701,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122154345</v>
+        <v>122152049</v>
       </c>
       <c r="B21" t="n">
-        <v>97165</v>
+        <v>79737</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2655,20 +2725,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>221945</v>
+        <v>6458</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2678,10 +2753,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>479596</v>
+        <v>479749</v>
       </c>
       <c r="R21" t="n">
-        <v>6951595</v>
+        <v>6951522</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2708,12 +2783,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2024-10-05</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2024-10-05</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2728,22 +2803,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122152039</v>
+        <v>122152041</v>
       </c>
       <c r="B22" t="n">
-        <v>79734</v>
+        <v>79737</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2756,16 +2831,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2081</v>
+        <v>6458</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2775,10 +2855,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>479768</v>
+        <v>479769</v>
       </c>
       <c r="R22" t="n">
-        <v>6951511</v>
+        <v>6951516</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2837,10 +2917,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122152076</v>
+        <v>122154346</v>
       </c>
       <c r="B23" t="n">
-        <v>79733</v>
+        <v>57536</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2853,29 +2933,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>103021</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Bergsvik, Jmt</t>
+          <t>Brynje, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>479653</v>
+        <v>479569</v>
       </c>
       <c r="R23" t="n">
-        <v>6951307</v>
+        <v>6951576</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -2902,12 +2987,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-10-05</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-10-05</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2922,22 +3007,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122152033</v>
+        <v>122152029</v>
       </c>
       <c r="B24" t="n">
-        <v>79733</v>
+        <v>79766</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2946,20 +3031,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>6462</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2969,10 +3059,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>479817</v>
+        <v>479816</v>
       </c>
       <c r="R24" t="n">
-        <v>6951441</v>
+        <v>6951443</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3031,10 +3121,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122152049</v>
+        <v>122152081</v>
       </c>
       <c r="B25" t="n">
-        <v>79733</v>
+        <v>79738</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3047,29 +3137,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>2081</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Skrovellav</t>
+        </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Brynje, Jmt</t>
+          <t>Bergsvik, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>479749</v>
+        <v>479613</v>
       </c>
       <c r="R25" t="n">
-        <v>6951522</v>
+        <v>6951267</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3128,10 +3223,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122152031</v>
+        <v>122152076</v>
       </c>
       <c r="B26" t="n">
-        <v>79734</v>
+        <v>79737</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3144,29 +3239,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2081</v>
+        <v>6458</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Brynje, Jmt</t>
+          <t>Bergsvik, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>479817</v>
+        <v>479653</v>
       </c>
       <c r="R26" t="n">
-        <v>6951441</v>
+        <v>6951307</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3225,10 +3325,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122152024</v>
+        <v>122152064</v>
       </c>
       <c r="B27" t="n">
-        <v>79734</v>
+        <v>98560</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3237,33 +3337,38 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2081</v>
+        <v>219880</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Kransrams</t>
+        </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Bergsvik, Jmt</t>
+          <t>Brynje, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>479764</v>
+        <v>479647</v>
       </c>
       <c r="R27" t="n">
-        <v>6951289</v>
+        <v>6951498</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3322,10 +3427,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122152042</v>
+        <v>122152033</v>
       </c>
       <c r="B28" t="n">
-        <v>79762</v>
+        <v>79737</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3334,20 +3439,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6462</v>
+        <v>6458</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3357,10 +3467,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>479757</v>
+        <v>479817</v>
       </c>
       <c r="R28" t="n">
-        <v>6951495</v>
+        <v>6951441</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3419,10 +3529,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122152026</v>
+        <v>122152077</v>
       </c>
       <c r="B29" t="n">
-        <v>79733</v>
+        <v>79737</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3437,6 +3547,11 @@
       <c r="E29" t="n">
         <v>6458</v>
       </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
       <c r="G29" t="inlineStr">
         <is>
           <t>Lobaria pulmonaria</t>
@@ -3454,10 +3569,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>479764</v>
+        <v>479619</v>
       </c>
       <c r="R29" t="n">
-        <v>6951290</v>
+        <v>6951287</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3516,10 +3631,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122152029</v>
+        <v>122152071</v>
       </c>
       <c r="B30" t="n">
-        <v>79762</v>
+        <v>79737</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3528,33 +3643,38 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6462</v>
+        <v>6458</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Brynje, Jmt</t>
+          <t>Bergsvik, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>479816</v>
+        <v>479656</v>
       </c>
       <c r="R30" t="n">
-        <v>6951443</v>
+        <v>6951332</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3613,10 +3733,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122152028</v>
+        <v>122152074</v>
       </c>
       <c r="B31" t="n">
-        <v>78652</v>
+        <v>79738</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3629,16 +3749,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>2081</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Skrovellav</t>
+        </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3648,10 +3773,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>479733</v>
+        <v>479654</v>
       </c>
       <c r="R31" t="n">
-        <v>6951321</v>
+        <v>6951309</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3710,10 +3835,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122152057</v>
+        <v>122152034</v>
       </c>
       <c r="B32" t="n">
-        <v>74758</v>
+        <v>79737</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3726,16 +3851,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1467</v>
+        <v>6458</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3745,10 +3875,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>479727</v>
+        <v>479844</v>
       </c>
       <c r="R32" t="n">
-        <v>6951580</v>
+        <v>6951363</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -3781,11 +3911,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2024-08-30</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>På granstubbe intill bäck.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3812,10 +3937,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122152023</v>
+        <v>122152021</v>
       </c>
       <c r="B33" t="n">
-        <v>56581</v>
+        <v>56593</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3824,25 +3949,30 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>102612</v>
+        <v>100138</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -3851,10 +3981,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>479776</v>
+        <v>479770</v>
       </c>
       <c r="R33" t="n">
-        <v>6951285</v>
+        <v>6951296</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -3887,6 +4017,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2024-08-30</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Uppflog.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3913,10 +4048,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122152064</v>
+        <v>122154345</v>
       </c>
       <c r="B34" t="n">
-        <v>98547</v>
+        <v>97178</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -3929,16 +4064,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>219880</v>
+        <v>221945</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3948,10 +4088,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>479647</v>
+        <v>479596</v>
       </c>
       <c r="R34" t="n">
-        <v>6951498</v>
+        <v>6951595</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -3978,12 +4118,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-10-05</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-10-05</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -3998,22 +4138,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122152079</v>
+        <v>122152050</v>
       </c>
       <c r="B35" t="n">
-        <v>79734</v>
+        <v>79738</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4028,6 +4168,11 @@
       <c r="E35" t="n">
         <v>2081</v>
       </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Skrovellav</t>
+        </is>
+      </c>
       <c r="G35" t="inlineStr">
         <is>
           <t>Lobaria scrobiculata</t>
@@ -4041,14 +4186,14 @@
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Bergsvik, Jmt</t>
+          <t>Brynje, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>479619</v>
+        <v>479716</v>
       </c>
       <c r="R35" t="n">
-        <v>6951287</v>
+        <v>6951549</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4107,10 +4252,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122152074</v>
+        <v>122152054</v>
       </c>
       <c r="B36" t="n">
-        <v>79734</v>
+        <v>79737</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4123,29 +4268,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>2081</v>
+        <v>6458</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Bergsvik, Jmt</t>
+          <t>Brynje, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>479654</v>
+        <v>479731</v>
       </c>
       <c r="R36" t="n">
-        <v>6951309</v>
+        <v>6951554</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4204,10 +4354,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122152073</v>
+        <v>122152042</v>
       </c>
       <c r="B37" t="n">
-        <v>79734</v>
+        <v>79766</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4216,33 +4366,38 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>2081</v>
+        <v>6462</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Bergsvik, Jmt</t>
+          <t>Brynje, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>479656</v>
+        <v>479757</v>
       </c>
       <c r="R37" t="n">
-        <v>6951332</v>
+        <v>6951495</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4301,10 +4456,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122152055</v>
+        <v>122152057</v>
       </c>
       <c r="B38" t="n">
-        <v>90813</v>
+        <v>74762</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4317,16 +4472,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1202</v>
+        <v>1467</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Rödbrun blekspik</t>
+        </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4336,10 +4496,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>479734</v>
+        <v>479727</v>
       </c>
       <c r="R38" t="n">
-        <v>6951563</v>
+        <v>6951580</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4372,6 +4532,11 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2024-08-30</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>På granstubbe intill bäck.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4398,10 +4563,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122154338</v>
+        <v>122152073</v>
       </c>
       <c r="B39" t="n">
-        <v>79733</v>
+        <v>79738</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4414,29 +4579,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6458</v>
+        <v>2081</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Skrovellav</t>
+        </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Brynje, Jmt</t>
+          <t>Bergsvik, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>479524</v>
+        <v>479656</v>
       </c>
       <c r="R39" t="n">
-        <v>6951553</v>
+        <v>6951332</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4463,12 +4633,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2024-10-05</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2024-10-05</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4483,22 +4653,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122152071</v>
+        <v>122152047</v>
       </c>
       <c r="B40" t="n">
-        <v>79733</v>
+        <v>79766</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4507,33 +4677,38 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6458</v>
+        <v>6462</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Bergsvik, Jmt</t>
+          <t>Brynje, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>479656</v>
+        <v>479750</v>
       </c>
       <c r="R40" t="n">
-        <v>6951332</v>
+        <v>6951517</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4592,10 +4767,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122152044</v>
+        <v>122154338</v>
       </c>
       <c r="B41" t="n">
-        <v>79734</v>
+        <v>79737</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4608,16 +4783,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>2081</v>
+        <v>6458</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4627,10 +4807,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>479757</v>
+        <v>479524</v>
       </c>
       <c r="R41" t="n">
-        <v>6951495</v>
+        <v>6951553</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -4657,12 +4837,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-10-05</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-10-05</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4677,22 +4857,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122152021</v>
+        <v>122152023</v>
       </c>
       <c r="B42" t="n">
-        <v>56589</v>
+        <v>56585</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4701,25 +4881,30 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100138</v>
+        <v>102612</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
@@ -4728,10 +4913,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>479770</v>
+        <v>479776</v>
       </c>
       <c r="R42" t="n">
-        <v>6951296</v>
+        <v>6951285</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -4764,11 +4949,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2024-08-30</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Uppflog.</t>
         </is>
       </c>
       <c r="AD42" t="b">

--- a/artfynd/A 18303-2024 artfynd.xlsx
+++ b/artfynd/A 18303-2024 artfynd.xlsx
@@ -1280,10 +1280,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122152068</v>
+        <v>122152081</v>
       </c>
       <c r="B7" t="n">
-        <v>95771</v>
+        <v>79738</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1296,34 +1296,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>53</v>
+        <v>2081</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Brynje, Jmt</t>
+          <t>Bergsvik, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>479630</v>
+        <v>479613</v>
       </c>
       <c r="R7" t="n">
-        <v>6951446</v>
+        <v>6951267</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1356,11 +1356,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-08-30</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>På murken granlåga i gransumpskog.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1387,10 +1382,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122152024</v>
+        <v>122152052</v>
       </c>
       <c r="B8" t="n">
-        <v>79738</v>
+        <v>79737</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1403,34 +1398,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Bergsvik, Jmt</t>
+          <t>Brynje, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>479764</v>
+        <v>479717</v>
       </c>
       <c r="R8" t="n">
-        <v>6951289</v>
+        <v>6951549</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1489,10 +1484,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122152055</v>
+        <v>122152026</v>
       </c>
       <c r="B9" t="n">
-        <v>90826</v>
+        <v>79737</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1505,34 +1500,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Brynje, Jmt</t>
+          <t>Bergsvik, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>479734</v>
+        <v>479764</v>
       </c>
       <c r="R9" t="n">
-        <v>6951563</v>
+        <v>6951290</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1591,10 +1586,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122152039</v>
+        <v>122152041</v>
       </c>
       <c r="B10" t="n">
-        <v>79738</v>
+        <v>79737</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1607,21 +1602,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1631,10 +1626,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>479768</v>
+        <v>479769</v>
       </c>
       <c r="R10" t="n">
-        <v>6951511</v>
+        <v>6951516</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1693,10 +1688,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122152037</v>
+        <v>122152031</v>
       </c>
       <c r="B11" t="n">
-        <v>79766</v>
+        <v>79738</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1705,25 +1700,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6462</v>
+        <v>2081</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1733,10 +1728,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>479767</v>
+        <v>479817</v>
       </c>
       <c r="R11" t="n">
-        <v>6951509</v>
+        <v>6951441</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1795,7 +1790,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122152031</v>
+        <v>122152079</v>
       </c>
       <c r="B12" t="n">
         <v>79738</v>
@@ -1831,14 +1826,14 @@
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Brynje, Jmt</t>
+          <t>Bergsvik, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>479817</v>
+        <v>479619</v>
       </c>
       <c r="R12" t="n">
-        <v>6951441</v>
+        <v>6951287</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1897,10 +1892,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122152045</v>
+        <v>122152037</v>
       </c>
       <c r="B13" t="n">
-        <v>79737</v>
+        <v>79766</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1909,25 +1904,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1937,10 +1932,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>479758</v>
+        <v>479767</v>
       </c>
       <c r="R13" t="n">
-        <v>6951496</v>
+        <v>6951509</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1999,10 +1994,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122152028</v>
+        <v>122154345</v>
       </c>
       <c r="B14" t="n">
-        <v>78656</v>
+        <v>97191</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2011,38 +2006,38 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Bergsvik, Jmt</t>
+          <t>Brynje, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>479733</v>
+        <v>479596</v>
       </c>
       <c r="R14" t="n">
-        <v>6951321</v>
+        <v>6951595</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2069,12 +2064,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-10-05</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-10-05</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2089,22 +2084,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122152142</v>
+        <v>122152024</v>
       </c>
       <c r="B15" t="n">
-        <v>78656</v>
+        <v>79738</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2117,21 +2112,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2141,10 +2136,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>479790</v>
+        <v>479764</v>
       </c>
       <c r="R15" t="n">
-        <v>6951160</v>
+        <v>6951289</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2171,12 +2166,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2203,10 +2198,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122152052</v>
+        <v>122152021</v>
       </c>
       <c r="B16" t="n">
-        <v>79737</v>
+        <v>56593</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2215,38 +2210,42 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>100138</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Brynje, Jmt</t>
+          <t>Bergsvik, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>479717</v>
+        <v>479770</v>
       </c>
       <c r="R16" t="n">
-        <v>6951549</v>
+        <v>6951296</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2279,6 +2278,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2024-08-30</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Uppflog.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2305,7 +2309,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122152079</v>
+        <v>122152073</v>
       </c>
       <c r="B17" t="n">
         <v>79738</v>
@@ -2345,10 +2349,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>479619</v>
+        <v>479656</v>
       </c>
       <c r="R17" t="n">
-        <v>6951287</v>
+        <v>6951332</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2407,10 +2411,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122152044</v>
+        <v>122152047</v>
       </c>
       <c r="B18" t="n">
-        <v>79738</v>
+        <v>79766</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2419,25 +2423,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2081</v>
+        <v>6462</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2447,10 +2451,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>479757</v>
+        <v>479750</v>
       </c>
       <c r="R18" t="n">
-        <v>6951495</v>
+        <v>6951517</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2509,10 +2513,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122152026</v>
+        <v>122152057</v>
       </c>
       <c r="B19" t="n">
-        <v>79737</v>
+        <v>74762</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2525,34 +2529,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>1467</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Bergsvik, Jmt</t>
+          <t>Brynje, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>479764</v>
+        <v>479727</v>
       </c>
       <c r="R19" t="n">
-        <v>6951290</v>
+        <v>6951580</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2585,6 +2589,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2024-08-30</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>På granstubbe intill bäck.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2611,10 +2620,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122154343</v>
+        <v>122154338</v>
       </c>
       <c r="B20" t="n">
-        <v>94250</v>
+        <v>79737</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2623,25 +2632,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2387</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Källpraktmossa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pseudobryum cinclidioides</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Huebener) T.J.Kop.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2651,10 +2660,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>479547</v>
+        <v>479524</v>
       </c>
       <c r="R20" t="n">
-        <v>6951577</v>
+        <v>6951553</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2713,7 +2722,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122152049</v>
+        <v>122152045</v>
       </c>
       <c r="B21" t="n">
         <v>79737</v>
@@ -2753,10 +2762,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>479749</v>
+        <v>479758</v>
       </c>
       <c r="R21" t="n">
-        <v>6951522</v>
+        <v>6951496</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2815,10 +2824,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122152041</v>
+        <v>122152064</v>
       </c>
       <c r="B22" t="n">
-        <v>79737</v>
+        <v>98573</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2827,25 +2836,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>219880</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2855,10 +2864,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>479769</v>
+        <v>479647</v>
       </c>
       <c r="R22" t="n">
-        <v>6951516</v>
+        <v>6951498</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3121,7 +3130,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122152081</v>
+        <v>122152039</v>
       </c>
       <c r="B25" t="n">
         <v>79738</v>
@@ -3157,14 +3166,14 @@
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Bergsvik, Jmt</t>
+          <t>Brynje, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>479613</v>
+        <v>479768</v>
       </c>
       <c r="R25" t="n">
-        <v>6951267</v>
+        <v>6951511</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3223,10 +3232,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122152076</v>
+        <v>122152028</v>
       </c>
       <c r="B26" t="n">
-        <v>79737</v>
+        <v>78656</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3239,21 +3248,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3263,10 +3272,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>479653</v>
+        <v>479733</v>
       </c>
       <c r="R26" t="n">
-        <v>6951307</v>
+        <v>6951321</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3325,10 +3334,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122152064</v>
+        <v>122152074</v>
       </c>
       <c r="B27" t="n">
-        <v>98560</v>
+        <v>79738</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3337,38 +3346,38 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>219880</v>
+        <v>2081</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Brynje, Jmt</t>
+          <t>Bergsvik, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>479647</v>
+        <v>479654</v>
       </c>
       <c r="R27" t="n">
-        <v>6951498</v>
+        <v>6951309</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3427,10 +3436,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122152033</v>
+        <v>122152142</v>
       </c>
       <c r="B28" t="n">
-        <v>79737</v>
+        <v>78656</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3443,34 +3452,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Brynje, Jmt</t>
+          <t>Bergsvik, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>479817</v>
+        <v>479790</v>
       </c>
       <c r="R28" t="n">
-        <v>6951441</v>
+        <v>6951160</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3497,12 +3506,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3529,7 +3538,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122152077</v>
+        <v>122152076</v>
       </c>
       <c r="B29" t="n">
         <v>79737</v>
@@ -3569,10 +3578,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>479619</v>
+        <v>479653</v>
       </c>
       <c r="R29" t="n">
-        <v>6951287</v>
+        <v>6951307</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3631,7 +3640,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122152071</v>
+        <v>122152077</v>
       </c>
       <c r="B30" t="n">
         <v>79737</v>
@@ -3671,10 +3680,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>479656</v>
+        <v>479619</v>
       </c>
       <c r="R30" t="n">
-        <v>6951332</v>
+        <v>6951287</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3733,7 +3742,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122152074</v>
+        <v>122152044</v>
       </c>
       <c r="B31" t="n">
         <v>79738</v>
@@ -3769,14 +3778,14 @@
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Bergsvik, Jmt</t>
+          <t>Brynje, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>479654</v>
+        <v>479757</v>
       </c>
       <c r="R31" t="n">
-        <v>6951309</v>
+        <v>6951495</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3835,7 +3844,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122152034</v>
+        <v>122152049</v>
       </c>
       <c r="B32" t="n">
         <v>79737</v>
@@ -3875,10 +3884,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>479844</v>
+        <v>479749</v>
       </c>
       <c r="R32" t="n">
-        <v>6951363</v>
+        <v>6951522</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -3937,10 +3946,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122152021</v>
+        <v>122152054</v>
       </c>
       <c r="B33" t="n">
-        <v>56593</v>
+        <v>79737</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3949,42 +3958,38 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100138</v>
+        <v>6458</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Bergsvik, Jmt</t>
+          <t>Brynje, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>479770</v>
+        <v>479731</v>
       </c>
       <c r="R33" t="n">
-        <v>6951296</v>
+        <v>6951554</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4017,11 +4022,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2024-08-30</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Uppflog.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4048,10 +4048,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122154345</v>
+        <v>122152055</v>
       </c>
       <c r="B34" t="n">
-        <v>97178</v>
+        <v>90839</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4060,25 +4060,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>221945</v>
+        <v>1202</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4088,10 +4088,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>479596</v>
+        <v>479734</v>
       </c>
       <c r="R34" t="n">
-        <v>6951595</v>
+        <v>6951563</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4118,12 +4118,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2024-10-05</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2024-10-05</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4138,22 +4138,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122152050</v>
+        <v>122152034</v>
       </c>
       <c r="B35" t="n">
-        <v>79738</v>
+        <v>79737</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4166,21 +4166,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4190,10 +4190,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>479716</v>
+        <v>479844</v>
       </c>
       <c r="R35" t="n">
-        <v>6951549</v>
+        <v>6951363</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4252,7 +4252,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122152054</v>
+        <v>122152033</v>
       </c>
       <c r="B36" t="n">
         <v>79737</v>
@@ -4292,10 +4292,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>479731</v>
+        <v>479817</v>
       </c>
       <c r="R36" t="n">
-        <v>6951554</v>
+        <v>6951441</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4456,10 +4456,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122152057</v>
+        <v>122152071</v>
       </c>
       <c r="B38" t="n">
-        <v>74762</v>
+        <v>79737</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4472,34 +4472,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1467</v>
+        <v>6458</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Brynje, Jmt</t>
+          <t>Bergsvik, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>479727</v>
+        <v>479656</v>
       </c>
       <c r="R38" t="n">
-        <v>6951580</v>
+        <v>6951332</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4532,11 +4532,6 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2024-08-30</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>På granstubbe intill bäck.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4563,10 +4558,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122152073</v>
+        <v>122154343</v>
       </c>
       <c r="B39" t="n">
-        <v>79738</v>
+        <v>94263</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4575,38 +4570,38 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>2081</v>
+        <v>2387</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Källpraktmossa</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Pseudobryum cinclidioides</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Huebener) T.J.Kop.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Bergsvik, Jmt</t>
+          <t>Brynje, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>479656</v>
+        <v>479547</v>
       </c>
       <c r="R39" t="n">
-        <v>6951332</v>
+        <v>6951577</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4633,12 +4628,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-10-05</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-10-05</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4653,22 +4648,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122152047</v>
+        <v>122152050</v>
       </c>
       <c r="B40" t="n">
-        <v>79766</v>
+        <v>79738</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4677,25 +4672,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6462</v>
+        <v>2081</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4705,10 +4700,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>479750</v>
+        <v>479716</v>
       </c>
       <c r="R40" t="n">
-        <v>6951517</v>
+        <v>6951549</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4767,10 +4762,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122154338</v>
+        <v>122152068</v>
       </c>
       <c r="B41" t="n">
-        <v>79737</v>
+        <v>95784</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4783,21 +4778,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6458</v>
+        <v>53</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4807,10 +4802,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>479524</v>
+        <v>479630</v>
       </c>
       <c r="R41" t="n">
-        <v>6951553</v>
+        <v>6951446</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -4837,12 +4832,17 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2024-10-05</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2024-10-05</t>
+          <t>2024-08-30</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>På murken granlåga i gransumpskog.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4857,12 +4857,12 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>

--- a/artfynd/A 18303-2024 artfynd.xlsx
+++ b/artfynd/A 18303-2024 artfynd.xlsx
@@ -1994,10 +1994,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122154345</v>
+        <v>122152021</v>
       </c>
       <c r="B14" t="n">
-        <v>97191</v>
+        <v>56593</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2010,34 +2010,38 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221945</v>
+        <v>100138</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Brynje, Jmt</t>
+          <t>Bergsvik, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>479596</v>
+        <v>479770</v>
       </c>
       <c r="R14" t="n">
-        <v>6951595</v>
+        <v>6951296</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2064,12 +2068,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-10-05</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-10-05</t>
+          <t>2024-08-30</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Uppflog.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2084,12 +2093,12 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -2198,10 +2207,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122152021</v>
+        <v>122154345</v>
       </c>
       <c r="B16" t="n">
-        <v>56593</v>
+        <v>97191</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2214,38 +2223,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100138</v>
+        <v>221945</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Bergsvik, Jmt</t>
+          <t>Brynje, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>479770</v>
+        <v>479596</v>
       </c>
       <c r="R16" t="n">
-        <v>6951296</v>
+        <v>6951595</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2272,17 +2277,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-10-05</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Uppflog.</t>
+          <t>2024-10-05</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2297,12 +2297,12 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
@@ -2513,10 +2513,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122152057</v>
+        <v>122154338</v>
       </c>
       <c r="B19" t="n">
-        <v>74762</v>
+        <v>79737</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2529,21 +2529,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1467</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2553,10 +2553,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>479727</v>
+        <v>479524</v>
       </c>
       <c r="R19" t="n">
-        <v>6951580</v>
+        <v>6951553</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2583,17 +2583,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-10-05</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>På granstubbe intill bäck.</t>
+          <t>2024-10-05</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2608,22 +2603,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122154338</v>
+        <v>122152057</v>
       </c>
       <c r="B20" t="n">
-        <v>79737</v>
+        <v>74762</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2636,21 +2631,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>1467</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2660,10 +2655,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>479524</v>
+        <v>479727</v>
       </c>
       <c r="R20" t="n">
-        <v>6951553</v>
+        <v>6951580</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2690,12 +2685,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2024-10-05</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2024-10-05</t>
+          <t>2024-08-30</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>På granstubbe intill bäck.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2710,12 +2710,12 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
@@ -2926,10 +2926,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122154346</v>
+        <v>122152039</v>
       </c>
       <c r="B23" t="n">
-        <v>57536</v>
+        <v>79738</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2942,21 +2942,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>103021</v>
+        <v>2081</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2966,10 +2966,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>479569</v>
+        <v>479768</v>
       </c>
       <c r="R23" t="n">
-        <v>6951576</v>
+        <v>6951511</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -2996,12 +2996,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2024-10-05</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2024-10-05</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3016,12 +3016,12 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
@@ -3130,10 +3130,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122152039</v>
+        <v>122154346</v>
       </c>
       <c r="B25" t="n">
-        <v>79738</v>
+        <v>57536</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3146,21 +3146,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2081</v>
+        <v>103021</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3170,10 +3170,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>479768</v>
+        <v>479569</v>
       </c>
       <c r="R25" t="n">
-        <v>6951511</v>
+        <v>6951576</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3200,12 +3200,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-10-05</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-10-05</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3220,12 +3220,12 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
@@ -4048,10 +4048,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122152055</v>
+        <v>122152034</v>
       </c>
       <c r="B34" t="n">
-        <v>90839</v>
+        <v>79737</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4064,21 +4064,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4088,10 +4088,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>479734</v>
+        <v>479844</v>
       </c>
       <c r="R34" t="n">
-        <v>6951563</v>
+        <v>6951363</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4150,7 +4150,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122152034</v>
+        <v>122152033</v>
       </c>
       <c r="B35" t="n">
         <v>79737</v>
@@ -4190,10 +4190,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>479844</v>
+        <v>479817</v>
       </c>
       <c r="R35" t="n">
-        <v>6951363</v>
+        <v>6951441</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4252,10 +4252,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122152033</v>
+        <v>122152042</v>
       </c>
       <c r="B36" t="n">
-        <v>79737</v>
+        <v>79766</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4264,25 +4264,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4292,10 +4292,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>479817</v>
+        <v>479757</v>
       </c>
       <c r="R36" t="n">
-        <v>6951441</v>
+        <v>6951495</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4354,10 +4354,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122152042</v>
+        <v>122152055</v>
       </c>
       <c r="B37" t="n">
-        <v>79766</v>
+        <v>90839</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4366,25 +4366,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6462</v>
+        <v>1202</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4394,10 +4394,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>479757</v>
+        <v>479734</v>
       </c>
       <c r="R37" t="n">
-        <v>6951495</v>
+        <v>6951563</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>

--- a/artfynd/A 18303-2024 artfynd.xlsx
+++ b/artfynd/A 18303-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY42"/>
+  <dimension ref="A1:AY51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>103968948</v>
+        <v>122152068</v>
       </c>
       <c r="B2" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,37 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Trätmyrbäcken, Jmt</t>
+          <t>Brynje, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>479815.9567162332</v>
+        <v>479630</v>
       </c>
       <c r="R2" t="n">
-        <v>6951438.603978445</v>
+        <v>6951446</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,22 +740,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2022-06-13</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>10:11</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2022-06-13</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>10:11</t>
+          <t>2024-08-30</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>På murken granlåga i gransumpskog.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -771,40 +761,26 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AS2" t="inlineStr">
-        <is>
-          <t>Jesper Wadstein</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Via Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>LstZ inventering av skogliga värdetrakter 2022</t>
-        </is>
-      </c>
+          <t>Johan Kjetselberg</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>103968947</v>
+        <v>103968943</v>
       </c>
       <c r="B3" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -812,21 +788,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>864</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -836,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>479616.8389986972</v>
+        <v>479653</v>
       </c>
       <c r="R3" t="n">
-        <v>6951286.008140163</v>
+        <v>6951378</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -871,7 +847,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -881,7 +857,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -917,53 +893,48 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>103968942</v>
+        <v>122152069</v>
       </c>
       <c r="B4" t="n">
-        <v>93044</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2809</v>
+        <v>864</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Trätmyrbäcken, Jmt</t>
+          <t>Brynje, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>479772.7497849981</v>
+        <v>479638</v>
       </c>
       <c r="R4" t="n">
-        <v>6951516.005163047</v>
+        <v>6951373</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -987,22 +958,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2022-06-13</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>10:15</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2022-06-13</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>10:15</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1013,40 +974,26 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AS4" t="inlineStr">
-        <is>
-          <t>Jesper Wadstein</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Via Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr">
-        <is>
-          <t>LstZ inventering av skogliga värdetrakter 2022</t>
-        </is>
-      </c>
+          <t>Johan Kjetselberg</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>103968945</v>
+        <v>122152141</v>
       </c>
       <c r="B5" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1054,37 +1001,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>864</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Nymyren, Jmt</t>
+          <t>Bergsvik, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>479649.3607613555</v>
+        <v>479667</v>
       </c>
       <c r="R5" t="n">
-        <v>6951265.603755419</v>
+        <v>6951188</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1108,22 +1055,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2022-06-13</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>10:01</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2022-06-13</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>10:01</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1134,40 +1071,26 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AS5" t="inlineStr">
-        <is>
-          <t>Jesper Wadstein</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Via Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr">
-        <is>
-          <t>LstZ inventering av skogliga värdetrakter 2022</t>
-        </is>
-      </c>
+          <t>Johan Kjetselberg</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>103968946</v>
+        <v>103968945</v>
       </c>
       <c r="B6" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1175,21 +1098,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2081</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1199,10 +1122,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>479631.0278563992</v>
+        <v>479649</v>
       </c>
       <c r="R6" t="n">
-        <v>6951275.359534292</v>
+        <v>6951265</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1234,7 +1157,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1244,7 +1167,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1280,15 +1203,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122152081</v>
+        <v>122152055</v>
       </c>
       <c r="B7" t="n">
-        <v>79738</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1296,34 +1214,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2081</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Bergsvik, Jmt</t>
+          <t>Brynje, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>479613</v>
+        <v>479734</v>
       </c>
       <c r="R7" t="n">
-        <v>6951267</v>
+        <v>6951563</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1382,15 +1300,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122152052</v>
+        <v>122152057</v>
       </c>
       <c r="B8" t="n">
-        <v>79737</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83312</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1398,21 +1311,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>1467</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1422,10 +1335,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>479717</v>
+        <v>479727</v>
       </c>
       <c r="R8" t="n">
-        <v>6951549</v>
+        <v>6951580</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1458,6 +1371,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-08-30</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>På granstubbe intill bäck.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1484,15 +1402,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122152026</v>
+        <v>103968946</v>
       </c>
       <c r="B9" t="n">
-        <v>79737</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1500,37 +1413,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Bergsvik, Jmt</t>
+          <t>Nymyren, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>479764</v>
+        <v>479631</v>
       </c>
       <c r="R9" t="n">
-        <v>6951290</v>
+        <v>6951275</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1554,12 +1467,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2022-06-13</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2022-06-13</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1570,31 +1493,35 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AS9" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr"/>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122152041</v>
+        <v>122152024</v>
       </c>
       <c r="B10" t="n">
-        <v>79737</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1602,34 +1529,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Brynje, Jmt</t>
+          <t>Bergsvik, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>479769</v>
+        <v>479764</v>
       </c>
       <c r="R10" t="n">
-        <v>6951516</v>
+        <v>6951289</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1691,12 +1618,7 @@
         <v>122152031</v>
       </c>
       <c r="B11" t="n">
-        <v>79738</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1790,15 +1712,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122152079</v>
+        <v>122152039</v>
       </c>
       <c r="B12" t="n">
-        <v>79738</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1826,14 +1743,14 @@
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Bergsvik, Jmt</t>
+          <t>Brynje, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>479619</v>
+        <v>479768</v>
       </c>
       <c r="R12" t="n">
-        <v>6951287</v>
+        <v>6951511</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1892,37 +1809,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122152037</v>
+        <v>122152044</v>
       </c>
       <c r="B13" t="n">
-        <v>79766</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6462</v>
+        <v>2081</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1932,10 +1844,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>479767</v>
+        <v>479757</v>
       </c>
       <c r="R13" t="n">
-        <v>6951509</v>
+        <v>6951495</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1994,54 +1906,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122152021</v>
+        <v>122152050</v>
       </c>
       <c r="B14" t="n">
-        <v>56593</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100138</v>
+        <v>2081</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Bergsvik, Jmt</t>
+          <t>Brynje, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>479770</v>
+        <v>479716</v>
       </c>
       <c r="R14" t="n">
-        <v>6951296</v>
+        <v>6951549</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2074,11 +1977,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2024-08-30</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Uppflog.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2105,15 +2003,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122152024</v>
+        <v>122152073</v>
       </c>
       <c r="B15" t="n">
-        <v>79738</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2145,10 +2038,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>479764</v>
+        <v>479656</v>
       </c>
       <c r="R15" t="n">
-        <v>6951289</v>
+        <v>6951332</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2207,50 +2100,45 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122154345</v>
+        <v>122152074</v>
       </c>
       <c r="B16" t="n">
-        <v>97191</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221945</v>
+        <v>2081</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Brynje, Jmt</t>
+          <t>Bergsvik, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>479596</v>
+        <v>479654</v>
       </c>
       <c r="R16" t="n">
-        <v>6951595</v>
+        <v>6951309</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2277,12 +2165,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-10-05</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-10-05</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2297,27 +2185,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122152073</v>
+        <v>122152079</v>
       </c>
       <c r="B17" t="n">
-        <v>79738</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2349,10 +2232,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>479656</v>
+        <v>479619</v>
       </c>
       <c r="R17" t="n">
-        <v>6951332</v>
+        <v>6951287</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2411,50 +2294,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122152047</v>
+        <v>122152081</v>
       </c>
       <c r="B18" t="n">
-        <v>79766</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6462</v>
+        <v>2081</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Brynje, Jmt</t>
+          <t>Bergsvik, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>479750</v>
+        <v>479613</v>
       </c>
       <c r="R18" t="n">
-        <v>6951517</v>
+        <v>6951267</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2513,37 +2391,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122154338</v>
+        <v>122154343</v>
       </c>
       <c r="B19" t="n">
-        <v>79737</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>95962</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>2387</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Källpraktmossa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pseudobryum cinclidioides</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Huebener) T.J.Kop.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2553,10 +2426,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>479524</v>
+        <v>479547</v>
       </c>
       <c r="R19" t="n">
-        <v>6951553</v>
+        <v>6951577</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2615,53 +2488,48 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122152057</v>
+        <v>103968942</v>
       </c>
       <c r="B20" t="n">
-        <v>74762</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96338</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1467</v>
+        <v>2809</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Brynje, Jmt</t>
+          <t>Trätmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>479727</v>
+        <v>479773</v>
       </c>
       <c r="R20" t="n">
-        <v>6951580</v>
+        <v>6951516</v>
       </c>
       <c r="S20" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2685,17 +2553,22 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2022-06-13</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>På granstubbe intill bäck.</t>
+          <t>2022-06-13</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2706,66 +2579,70 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
+      </c>
+      <c r="AS20" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
+        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
-        </is>
-      </c>
-      <c r="AY20" t="inlineStr"/>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122152045</v>
+        <v>122152028</v>
       </c>
       <c r="B21" t="n">
-        <v>79737</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Brynje, Jmt</t>
+          <t>Bergsvik, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>479758</v>
+        <v>479733</v>
       </c>
       <c r="R21" t="n">
-        <v>6951496</v>
+        <v>6951321</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2824,50 +2701,45 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122152064</v>
+        <v>122152142</v>
       </c>
       <c r="B22" t="n">
-        <v>98573</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>219880</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Brynje, Jmt</t>
+          <t>Bergsvik, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>479647</v>
+        <v>479790</v>
       </c>
       <c r="R22" t="n">
-        <v>6951498</v>
+        <v>6951160</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2894,12 +2766,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2926,37 +2798,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122152039</v>
+        <v>122154336</v>
       </c>
       <c r="B23" t="n">
-        <v>79738</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2966,10 +2833,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>479768</v>
+        <v>479513</v>
       </c>
       <c r="R23" t="n">
-        <v>6951511</v>
+        <v>6951613</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -2996,12 +2863,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-10-05</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-10-05</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3016,62 +2883,57 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122152029</v>
+        <v>122152139</v>
       </c>
       <c r="B24" t="n">
-        <v>79766</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6462</v>
+        <v>6453</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Brynje, Jmt</t>
+          <t>Bergsvik, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>479816</v>
+        <v>479649</v>
       </c>
       <c r="R24" t="n">
-        <v>6951443</v>
+        <v>6951187</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3098,12 +2960,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3130,15 +2992,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122154346</v>
+        <v>103968947</v>
       </c>
       <c r="B25" t="n">
-        <v>57536</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3146,37 +3003,37 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Brynje, Jmt</t>
+          <t>Nymyren, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>479569</v>
+        <v>479617</v>
       </c>
       <c r="R25" t="n">
-        <v>6951576</v>
+        <v>6951286</v>
       </c>
       <c r="S25" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3200,12 +3057,22 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2024-10-05</t>
+          <t>2022-06-13</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2024-10-05</t>
+          <t>2022-06-13</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3216,31 +3083,35 @@
       </c>
       <c r="AG25" t="b">
         <v>0</v>
+      </c>
+      <c r="AS25" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
+        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
-        </is>
-      </c>
-      <c r="AY25" t="inlineStr"/>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122152028</v>
+        <v>103968948</v>
       </c>
       <c r="B26" t="n">
-        <v>78656</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3248,37 +3119,37 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Bergsvik, Jmt</t>
+          <t>Trätmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>479733</v>
+        <v>479816</v>
       </c>
       <c r="R26" t="n">
-        <v>6951321</v>
+        <v>6951438</v>
       </c>
       <c r="S26" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3302,12 +3173,22 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2022-06-13</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2022-06-13</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3318,31 +3199,35 @@
       </c>
       <c r="AG26" t="b">
         <v>0</v>
+      </c>
+      <c r="AS26" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
+        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
-        </is>
-      </c>
-      <c r="AY26" t="inlineStr"/>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122152074</v>
+        <v>122152026</v>
       </c>
       <c r="B27" t="n">
-        <v>79738</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3350,21 +3235,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3374,10 +3259,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>479654</v>
+        <v>479764</v>
       </c>
       <c r="R27" t="n">
-        <v>6951309</v>
+        <v>6951290</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3436,15 +3321,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122152142</v>
+        <v>122152033</v>
       </c>
       <c r="B28" t="n">
-        <v>78656</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3452,34 +3332,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Bergsvik, Jmt</t>
+          <t>Brynje, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>479790</v>
+        <v>479817</v>
       </c>
       <c r="R28" t="n">
-        <v>6951160</v>
+        <v>6951441</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3506,12 +3386,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3538,15 +3418,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122152076</v>
+        <v>122152034</v>
       </c>
       <c r="B29" t="n">
-        <v>79737</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3574,14 +3449,14 @@
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Bergsvik, Jmt</t>
+          <t>Brynje, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>479653</v>
+        <v>479844</v>
       </c>
       <c r="R29" t="n">
-        <v>6951307</v>
+        <v>6951363</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3640,15 +3515,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122152077</v>
+        <v>122152041</v>
       </c>
       <c r="B30" t="n">
-        <v>79737</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3676,14 +3546,14 @@
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Bergsvik, Jmt</t>
+          <t>Brynje, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>479619</v>
+        <v>479769</v>
       </c>
       <c r="R30" t="n">
-        <v>6951287</v>
+        <v>6951516</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3742,15 +3612,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122152044</v>
+        <v>122152045</v>
       </c>
       <c r="B31" t="n">
-        <v>79738</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3758,21 +3623,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3782,10 +3647,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>479757</v>
+        <v>479758</v>
       </c>
       <c r="R31" t="n">
-        <v>6951495</v>
+        <v>6951496</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3847,12 +3712,7 @@
         <v>122152049</v>
       </c>
       <c r="B32" t="n">
-        <v>79737</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3946,15 +3806,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122152054</v>
+        <v>122152052</v>
       </c>
       <c r="B33" t="n">
-        <v>79737</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3986,10 +3841,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>479731</v>
+        <v>479717</v>
       </c>
       <c r="R33" t="n">
-        <v>6951554</v>
+        <v>6951549</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4048,15 +3903,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122152034</v>
+        <v>122152054</v>
       </c>
       <c r="B34" t="n">
-        <v>79737</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4088,10 +3938,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>479844</v>
+        <v>479731</v>
       </c>
       <c r="R34" t="n">
-        <v>6951363</v>
+        <v>6951554</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4150,15 +4000,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122152033</v>
+        <v>122152071</v>
       </c>
       <c r="B35" t="n">
-        <v>79737</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4186,14 +4031,14 @@
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Brynje, Jmt</t>
+          <t>Bergsvik, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>479817</v>
+        <v>479656</v>
       </c>
       <c r="R35" t="n">
-        <v>6951441</v>
+        <v>6951332</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4252,50 +4097,45 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122152042</v>
+        <v>122152076</v>
       </c>
       <c r="B36" t="n">
-        <v>79766</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Brynje, Jmt</t>
+          <t>Bergsvik, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>479757</v>
+        <v>479653</v>
       </c>
       <c r="R36" t="n">
-        <v>6951495</v>
+        <v>6951307</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4354,15 +4194,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122152055</v>
+        <v>122152077</v>
       </c>
       <c r="B37" t="n">
-        <v>90839</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4370,34 +4205,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Brynje, Jmt</t>
+          <t>Bergsvik, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>479734</v>
+        <v>479619</v>
       </c>
       <c r="R37" t="n">
-        <v>6951563</v>
+        <v>6951287</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4456,15 +4291,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122152071</v>
+        <v>122154331</v>
       </c>
       <c r="B38" t="n">
-        <v>79737</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4492,14 +4322,14 @@
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Bergsvik, Jmt</t>
+          <t>Brynje, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>479656</v>
+        <v>479485</v>
       </c>
       <c r="R38" t="n">
-        <v>6951332</v>
+        <v>6951601</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4526,12 +4356,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-10-05</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-10-05</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4546,49 +4376,44 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122154343</v>
+        <v>122154337</v>
       </c>
       <c r="B39" t="n">
-        <v>94263</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>2387</v>
+        <v>6458</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Källpraktmossa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Pseudobryum cinclidioides</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Huebener) T.J.Kop.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4598,10 +4423,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>479547</v>
+        <v>479511</v>
       </c>
       <c r="R39" t="n">
-        <v>6951577</v>
+        <v>6951529</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4660,15 +4485,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122152050</v>
+        <v>122154338</v>
       </c>
       <c r="B40" t="n">
-        <v>79738</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4676,21 +4496,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4700,10 +4520,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>479716</v>
+        <v>479524</v>
       </c>
       <c r="R40" t="n">
-        <v>6951549</v>
+        <v>6951553</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4730,12 +4550,12 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-10-05</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-10-05</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4750,49 +4570,44 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122152068</v>
+        <v>122152029</v>
       </c>
       <c r="B41" t="n">
-        <v>95784</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>53</v>
+        <v>6462</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4802,10 +4617,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>479630</v>
+        <v>479816</v>
       </c>
       <c r="R41" t="n">
-        <v>6951446</v>
+        <v>6951443</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -4838,11 +4653,6 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2024-08-30</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>På murken granlåga i gransumpskog.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4869,54 +4679,45 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122152023</v>
+        <v>122152037</v>
       </c>
       <c r="B42" t="n">
-        <v>56585</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>102612</v>
+        <v>6462</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Bergsvik, Jmt</t>
+          <t>Brynje, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>479776</v>
+        <v>479767</v>
       </c>
       <c r="R42" t="n">
-        <v>6951285</v>
+        <v>6951509</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -4972,6 +4773,911 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>122152042</v>
+      </c>
+      <c r="B43" t="n">
+        <v>80461</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Brynje, Jmt</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>479757</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6951495</v>
+      </c>
+      <c r="S43" t="n">
+        <v>5</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2024-08-30</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2024-08-30</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Johan Kjetselberg</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Johan Kjetselberg</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>122152047</v>
+      </c>
+      <c r="B44" t="n">
+        <v>80461</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Brynje, Jmt</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>479750</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6951517</v>
+      </c>
+      <c r="S44" t="n">
+        <v>5</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2024-08-30</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2024-08-30</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Johan Kjetselberg</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Johan Kjetselberg</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>103968949</v>
+      </c>
+      <c r="B45" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Nymyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>479696</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6951254</v>
+      </c>
+      <c r="S45" t="n">
+        <v>10</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2022-06-13</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>10:04</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2022-06-13</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>10:04</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AS45" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
+        </is>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>122152021</v>
+      </c>
+      <c r="B46" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Bergsvik, Jmt</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>479770</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6951296</v>
+      </c>
+      <c r="S46" t="n">
+        <v>5</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2024-08-30</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2024-08-30</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Uppflog.</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Johan Kjetselberg</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Johan Kjetselberg</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>122152023</v>
+      </c>
+      <c r="B47" t="n">
+        <v>57132</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>102612</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Bergsvik, Jmt</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>479776</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6951285</v>
+      </c>
+      <c r="S47" t="n">
+        <v>5</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2024-08-30</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2024-08-30</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Johan Kjetselberg</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Johan Kjetselberg</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>122154346</v>
+      </c>
+      <c r="B48" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Brynje, Jmt</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>479569</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6951576</v>
+      </c>
+      <c r="S48" t="n">
+        <v>5</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2024-10-05</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2024-10-05</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Ward Tamsyn</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Ward Tamsyn</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>122152064</v>
+      </c>
+      <c r="B49" t="n">
+        <v>99456</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>219880</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Kransrams</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Polygonatum verticillatum</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(L.) All.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Brynje, Jmt</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>479647</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6951498</v>
+      </c>
+      <c r="S49" t="n">
+        <v>5</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2024-08-30</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2024-08-30</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Johan Kjetselberg</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Johan Kjetselberg</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>122152036</v>
+      </c>
+      <c r="B50" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Brynje, Jmt</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>479844</v>
+      </c>
+      <c r="R50" t="n">
+        <v>6951555</v>
+      </c>
+      <c r="S50" t="n">
+        <v>5</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2024-08-30</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2024-08-30</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Johan Kjetselberg</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Johan Kjetselberg</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>122154345</v>
+      </c>
+      <c r="B51" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Brynje, Jmt</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>479596</v>
+      </c>
+      <c r="R51" t="n">
+        <v>6951595</v>
+      </c>
+      <c r="S51" t="n">
+        <v>5</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2024-10-05</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2024-10-05</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Ward Tamsyn</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Ward Tamsyn</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 18303-2024 artfynd.xlsx
+++ b/artfynd/A 18303-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY51"/>
+  <dimension ref="A1:AZ51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122152068</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -890,6 +900,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103968943</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -987,6 +1002,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122152069</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1084,6 +1104,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122152141</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1200,6 +1225,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103968945</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1297,6 +1327,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122152055</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1399,6 +1434,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122152057</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1515,6 +1555,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103968946</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1612,6 +1657,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122152024</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1709,6 +1759,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122152031</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1806,6 +1861,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122152039</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1903,6 +1963,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122152044</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2000,6 +2065,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122152050</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2097,6 +2167,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122152073</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2194,6 +2269,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122152074</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2291,6 +2371,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122152079</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2388,6 +2473,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122152081</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2485,6 +2575,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122154343</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2601,6 +2696,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103968942</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2698,6 +2798,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122152028</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2795,6 +2900,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122152142</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2892,6 +3002,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122154336</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2989,6 +3104,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122152139</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3105,6 +3225,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103968947</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3221,6 +3346,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103968948</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3318,6 +3448,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122152026</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3415,6 +3550,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122152033</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3512,6 +3652,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122152034</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3609,6 +3754,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122152041</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3706,6 +3856,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122152045</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3803,6 +3958,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122152049</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3900,6 +4060,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122152052</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3997,6 +4162,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122152054</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4094,6 +4264,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122152071</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4191,6 +4366,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122152076</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4288,6 +4468,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122152077</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4385,6 +4570,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122154331</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4482,6 +4672,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122154337</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4579,6 +4774,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122154338</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4676,6 +4876,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122152029</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4773,6 +4978,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122152037</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4870,6 +5080,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122152042</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -4967,6 +5182,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122152047</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5083,6 +5303,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103968949</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5189,6 +5414,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122152021</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5290,6 +5520,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122152023</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5387,6 +5622,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122154346</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5484,6 +5724,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122152064</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5581,6 +5826,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122152036</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5678,8 +5928,65 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122154345</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>